--- a/Full Adult Version/REACH - FAV_codebook_20May2026.xlsx
+++ b/Full Adult Version/REACH - FAV_codebook_20May2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huntlc/Documents/REACH Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C9410C-C0A4-6647-9715-81CF27B4D860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F4A77CF-CDDB-744D-90C5-17EE158E1517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45720" yWindow="600" windowWidth="27240" windowHeight="16180" xr2:uid="{DC13C6BE-47AD-594D-B3E9-96CB9381A8CF}"/>
+    <workbookView xWindow="34580" yWindow="600" windowWidth="19200" windowHeight="21000" xr2:uid="{DC13C6BE-47AD-594D-B3E9-96CB9381A8CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="863">
   <si>
     <t>Full Adult/Adolescent version to be used for persons ages 12 or older</t>
   </si>
@@ -777,10 +777,6 @@
   </si>
   <si>
     <t xml:space="preserve">If time on the Internet &gt; 0 minutes
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chat rooms (0,1), Blogs (0,1), Music (Spotify, iTunes, etc (0,1), News (0,1), Direct messenger (0,1), Gaming (0,1), Shopping (0,1), Social media (0,1), Web browsing (0,1), Internet TV (Netflix, Hulu, etc) (0,1), Work/school (0,1)
 </t>
   </si>
   <si>
@@ -3109,12 +3105,273 @@
   <si>
     <t>ema_clean only; 1 or 0. Manually added flags for any other reasons (eg.- low staffing during holiday periods, etc.). Will be 1 for all assessments for each of the flagged individuals.</t>
   </si>
+  <si>
+    <t>For what did you use the internet?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI chatbot (e.g., ChatGPT, Gemini, Claude, Meta AI, Copilot, or an AI companion) (0,1), Chat rooms (0,1), Blogs (0,1), Music (Spotify, iTunes, etc (0,1), News (0,1), Direct messenger (0,1), Gaming (0,1), Shopping (0,1), Social media (0,1), Web browsing (0,1), Internet TV (Netflix, Hulu, etc) (0,1), Work/school (0,1)
+</t>
+  </si>
+  <si>
+    <t>ai_chatbot_duration</t>
+  </si>
+  <si>
+    <t>ai_chatbot_category</t>
+  </si>
+  <si>
+    <t>ai_chatbot_category_other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Since the last assessment, how much time did you spend text-chatting, speaking with, or asking for advice from and AI chatbot or AI assistant? </t>
+  </si>
+  <si>
+    <t>if internet_use_category %includes% AI Chatbot</t>
+  </si>
+  <si>
+    <t>What was the primary reason you used the chatbot?</t>
+  </si>
+  <si>
+    <t>Information Seeking (looking up facts, explanations, trivia, or quick answers) (1)
+Emotional Support &amp; Companionship (venting, seeking comfort, validation, or just passing the time chatting) (2)
+Personal Advice &amp; Decision Making (seeking guidance on a personal dilemma, life choices, or relationships) (3)
+Task Assistance (getting help with work, writing, or technical troubleshooting) (4)
+Entertainment or Creative Fun (generating images, roleplaying, brainstorming for amusement) (5)
+Other (6)</t>
+  </si>
+  <si>
+    <t>Please specify the other reason you used the AI chatbot.</t>
+  </si>
+  <si>
+    <t>if ai_chatbot_category %equals% Other</t>
+  </si>
+  <si>
+    <t>If you were using an AI chatbot, this question asks you to indicate how much time you spent using the Chatbot since the last assessment. Please select one response.</t>
+  </si>
+  <si>
+    <t>If you were using an AI chatbot, this question asks you to indicate what you used the chatbot for. You can select multiple responses.</t>
+  </si>
+  <si>
+    <t>If you used an AI chatbot for another reason other than those listed, here you are asked to specify in a short text response what that other reason was.</t>
+  </si>
+  <si>
+    <t>Response Values</t>
+  </si>
+  <si>
+    <t>No: 0 (score: 0), Yes: 1 (score: 1)</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>None: 0 (score: 0), Once: 1 (score: 1), Twice: 2 (score: 2), Three or More Times: 3 (score: 3)</t>
+  </si>
+  <si>
+    <t>Less Than 30 Minutes: 0 (score: 0), 30-60 Minutes: 1 (score: 1), 60-120 Minutes: 2 (score: 2), Longer Than 120 Minutes: 3 (score: 3)</t>
+  </si>
+  <si>
+    <t>1: 1 (score: 1), 2: 2 (score: 2), 3: 3 (score: 3), 4: 4 (score: 4), 5: 5 (score: 5), 6: 6 (score: 6), 7: 7 (score: 7)</t>
+  </si>
+  <si>
+    <t>Difficulty falling asleep: 0 (score: 1), Awakening too early: 1 (score: 2), Feeling unrefreshed or unrestored despite enough hours of sleep: 2 (score: 3), Nightmares: 3 (score: 4), Other sleep problem: 4 (score: 5), None of the above: 5 (score: 6)</t>
+  </si>
+  <si>
+    <t>Prescribed Medication (sleeping pill): 0 (score: 0), Prescribed Medication (antidepressant): 1 (score: 1), Prescribed Medication (other): 2 (score: 2), Unprescribed Medication (Melatonin): 3 (score: 3), Unprescribed Medication (Antihistamine): 4 (score: 4), Unprescribed Medication (Other): 5 (score: 5)</t>
+  </si>
+  <si>
+    <t>geo: lat/long</t>
+  </si>
+  <si>
+    <t>Inside: 0 (score: 0), Outside: 1 (score: 1)</t>
+  </si>
+  <si>
+    <t>In your home: 0 (score: 1), In home of relative or friend: 1 (score: 2), At work or in class: 2 (score: 3), In a restaurant/bar or in a store : 3 (score: 4), In a gym or fitness center: 4 (score: 5), In a hospital or doctor’s office : 5 (score: 6), Other place inside: 6 (score: 7)</t>
+  </si>
+  <si>
+    <t>In a public park or garden: 0 (score: 1), In your yard or at home: 1 (score: 2), In your neighborhood: 3 (score: 3), At school: 4 (score: 4), In a vehicle (car, bus…) : 5 (score: 5), In other place outside: 6 (score: 6)</t>
+  </si>
+  <si>
+    <t>Inside: 0 (score: 1), Outside: 1 (score: 2)</t>
+  </si>
+  <si>
+    <t>In your home: 0 (score: 1), In home of relative or friend : 1 (score: 2), At work or in class : 2 (score: 3), In a restaurant/bar or in a store: 3 (score: 4), In a gym or fitness center: 4 (score: 5), In a hospital or doctor’s office: 5 (score: 6), Other place inside: 6 (score: 7)</t>
+  </si>
+  <si>
+    <t>In a public park or garden: 0 (score: 1), In your yard or at home: 1 (score: 2), In your neighborhood: 2 (score: 3), At school: 3 (score: 4), In a vehicle (e.g., car, bus): 4 (score: 5), In other place outside: 5 (score: 6)</t>
+  </si>
+  <si>
+    <t>No one: 0 (score: 1), A family member: 1 (score: 2), Your romantic partner: 2 (score: 3), Friends: 3 (score: 4), Colleagues or classmates: 4 (score: 5), Strangers: 5 (score: 6), Healthcare provider: 6 (score: 7), Pets: 7 (score: 8)</t>
+  </si>
+  <si>
+    <t>Working or studying: 0 (score: 1), Socializing in person: 1 (score: 2), Using your phone: 2 (score: 3), Watching TV/videos, playing video games, reading: 3 (score: 4), Traveling or commuting: 4 (score: 5), Household chores, shopping: 5 (score: 6), Physical exercise: 6 (score: 7), Eating/drinking: 7 (score: 8), Personal hygiene care: 8 (score: 9), Medical procedure or treatment: 9 (score: 10), Nothing, resting: 10 (score: 11), Other activity: 11 (score: 12)</t>
+  </si>
+  <si>
+    <t>geolocation</t>
+  </si>
+  <si>
+    <t>I did not use a computer, tablet, phone or watch TV: 0 (score: 0), Less Than 1 Hour: 1 (score: 1), 1-2 Hours: 2 (score: 2), 2-3 Hours: 3 (score: 3), 3-4 Hours: 4 (score: 4), More Than 4 Hours: 5 (score: 5)</t>
+  </si>
+  <si>
+    <t>I did not use the Internet : 0 (score: 0), Less Than 1 Hour: 1 (score: 1), 1-2 Hours: 2 (score: 2), 2-3 Hours: 3 (score: 3), 3-4 Hours: 4 (score: 4), More Than 4 Hours: 5 (score: 5)</t>
+  </si>
+  <si>
+    <t>Less Than 1 Hour: 1 (score: 1), 1-2 Hours: 2 (score: 2), 2-3 Hours: 3 (score: 3), 3-4 Hours: 4 (score: 4), More Than 4 Hours: 5 (score: 5)</t>
+  </si>
+  <si>
+    <t>Posted pictures or videos of yourself : 0 (score: 1), Posted pictures or videos of other people: 1 (score: 2), Read comments made by others on your content : 2 (score: 3), Posted comments on other peoples’ content: 3 (score: 4), Checked the number of followers/subscribers/likes you have : 4 (score: 5), Communicated with people you know : 5 (score: 6), Communicated with people you don’t know or only know online: 6 (score: 7), None of the above: 7 (score: 8)</t>
+  </si>
+  <si>
+    <t>By text, email, instant messaging: 0 (score: 1), By video, video chat, facetime, zoom: 1 (score: 2)</t>
+  </si>
+  <si>
+    <t>AI chatbot (e.g., ChatGPT, Gemini, Claude, Meta AI, Copilot, or an AI companion): 0 (score: 12), Chat rooms: 1 (score: 1), Blogs: 2 (score: 2), Music (Spotify, iTunes, etc): 3 (score: 3), News: 4 (score: 4), Direct messenger: 5 (score: 5), Gaming: 6 (score: 6), Shopping: 7 (score: 7), Social media: 8 (score: 8), Web browsing: 9 (score: 9), Internet TV (Netflix, Hulu, etc): 10 (score: 10), Work/school: 11 (score: 11)</t>
+  </si>
+  <si>
+    <t>Less Than 1 Hour: 0 (score: 1), 1-2 Hours: 1 (score: 2), 2-3 Hours: 2 (score: 3), 3-4 Hours: 3 (score: 4), More Than 4 Hours: 4 (score: 5)</t>
+  </si>
+  <si>
+    <t>Information Seeking (looking up facts, explanations, trivia, or quick answers) : 0 (score: 1), Emotional Support &amp; Companionship (venting, seeking comfort, validation, or just passing the time chatting): 1 (score: 2), Personal Advice &amp; Decision Making (seeking guidance on a personal dilemma, life choices, or relationships): 2 (score: 3), Task Assistance (getting help with work, writing, or technical troubleshooting): 3 (score: 4), Entertainment or Creative Fun (generating images, roleplaying, brainstorming for amusement): 4 (score: 5), Other: 5 (score: 6)</t>
+  </si>
+  <si>
+    <t>Things you did that you regret: 0 (score: 1), Things that happened to you: 1 (score: 2), Things that happened to others: 2 (score: 3), Worries that you have: 3 (score: 4)</t>
+  </si>
+  <si>
+    <t>By selecting this button, you acknowledge the statement above.: 0</t>
+  </si>
+  <si>
+    <t>Social interactions in-person: 0 (score: 1), Social interactions online/on the phone: 1 (score: 2), Accomplishment/getting things done: 2 (score: 3), Health event/medical care: 3 (score: 4), Learning about or witnessing something upsetting or something heartwarming: 4 (score: 5), Other: 5 (score: 6)</t>
+  </si>
+  <si>
+    <t>People at work or at school : 0 (score: 1), Romantic partner: 1 (score: 2), Your parents: 2 (score: 3), Your children: 3 (score: 4), Other family members: 4 (score: 5), Friends: 5 (score: 6), Acquaintances: 6 (score: 7), Strangers: 7 (score: 8)</t>
+  </si>
+  <si>
+    <t>At work or at school: 0 (score: 1), At home (chores, project): 1 (score: 2), Running errands: 2 (score: 3), Sports or exercise: 3 (score: 4)</t>
+  </si>
+  <si>
+    <t>Discomfort: 0 (score: 1), Medication-related event: 1 (score: 2), Medical appointment: 2 (score: 3), Alcohol or drug-related event: 3 (score: 4)</t>
+  </si>
+  <si>
+    <t>Learning about something upsetting on social media or online: 0 (score: 1), Learning about something upsetting in person: 1 (score: 2), Witnessing something upsetting: 2 (score: 3), Learning about something heartwarming on social media or online: 3 (score: 4), Learning about something heartwarming in person: 4 (score: 5), Witnessing something heartwarming: 5 (score: 6)</t>
+  </si>
+  <si>
+    <t>Transportation, travel or commute: 0 (score: 1), Financial issues: 1 (score: 2), Legal issues: 2 (score: 3), Religion/spirituality: 3 (score: 4), Leisure: 4 (score: 5), Other: 5 (score: 6)</t>
+  </si>
+  <si>
+    <t>Vigorous activities (e.g. running, fast cycling, heavy lifting or digging): 0 (score: 1), Moderate activities (e.g. bicycling, carrying light loads): 1 (score: 2), Light activities (e.g. walking, climbing stairs, routine household chores) : 2 (score: 3), Sedentary activites (e.g. napping, resting, or sitting): 3 (score: 4)</t>
+  </si>
+  <si>
+    <t>Napping: 0 (score: 1), Resting: 1 (score: 2), Sitting: 2 (score: 3)</t>
+  </si>
+  <si>
+    <t>time picker</t>
+  </si>
+  <si>
+    <t>About 5 Minutes or Less: 0 (score: 0), About 10 Minutes: 1 (score: 1), About 20 Minutes: 2 (score: 2), About 30 Minutes: 3 (score: 3), About 40 Minutes: 4 (score: 4), About 50 Minutes: 5 (score: 5), More Than 1 Hour: 6 (score: 6)</t>
+  </si>
+  <si>
+    <t>Water: 0 (score: 1), Milk: 1 (score: 2), A caffeinated beverage (like coffee, tea, soda…) : 2 (score: 3), An alcoholic beverage (wine, beer, liquor…): 3 (score: 4), A beverage containing sugar like juice or caffeine free soda: 4 (score: 5), Another type of drink: 5 (score: 6), I did not drink: 6 (score: 7)</t>
+  </si>
+  <si>
+    <t>1 8-oz Glass: 1 (score: 1), 2 8-oz Glasses: 2 (score: 2), 3 8-oz Glasses: 3 (score: 3), 4 8-oz Glasses: 4 (score: 4), 5 8-oz Glasses: 5 (score: 5), 6 8-oz Glasses: 6 (score: 6), 7 8-oz Glasses: 7 (score: 7), 8 8-oz Glasses: 8 (score: 8), 9 8-oz Glasses: 9 (score: 9), 10 or More 8-oz Glasses: 10 (score: 10)</t>
+  </si>
+  <si>
+    <t>Red Wine: 0 (score: 1), White Wine: 1 (score: 2), Champagne/ Sparkling Wine: 2 (score: 3), Beer: 3 (score: 4), Cocktail: 4 (score: 5), Whisky: 5 (score: 6), Other Type of Alcoholic Drink: 6 (score: 7)</t>
+  </si>
+  <si>
+    <t>1 Serving: 1 (score: 1), 2 Servings: 2 (score: 2), 3 Servings: 3 (score: 3), 4 Serving: 4 (score: 4), 5 Servings: 5 (score: 5), 6 Servings: 6 (score: 6), 7 Servings: 7 (score: 7), 8 Servings: 8 (score: 8), 9 Servings: 9 (score: 9), 10 or More Servings: 10 (score: 10)</t>
+  </si>
+  <si>
+    <t>Soda (Coke, Pepsi, other caffeinated soda): 0 (score: 1), Energy drink: 1 (score: 2), Coffee: 2 (score: 3), Tea: 3 (score: 4), Other: 4 (score: 5)</t>
+  </si>
+  <si>
+    <t>None: 0 (score: 0), 1: 1 (score: 1), 2: 2 (score: 2), 3: 3 (score: 3), 4: 4 (score: 4), 5: 5 (score: 5), 6: 6 (score: 6), 7: 7 (score: 7), 8: 8 (score: 8), 9: 9 (score: 9), 10: 10 (score: 10)</t>
+  </si>
+  <si>
+    <t>Just a Snack: 1 (score: 1), Continuous Snacking: 2 (score: 2), A Small Meal: 3 (score: 3), A Regular/Full Meal: 4 (score: 4), A Large Meal: 5 (score: 5)</t>
+  </si>
+  <si>
+    <t>Meat, Poultry, Fish: 1 (score: 1), Dairy, Eggs: 2 (score: 2), Fruits, Vegetables: 3 (score: 3), Snack Foods, Desserts: 4 (score: 4), Bread, Grains, Cereals: 5 (score: 5)</t>
+  </si>
+  <si>
+    <t>Beef, pork, ham, bacon, sausage: 1 (score: 1), Chicken, turkey, duck: 2 (score: 2), Fish, seafood: 3 (score: 3), Other Meat, Poultry, Fish Products: 4 (score: 4)</t>
+  </si>
+  <si>
+    <t>Cheese: 1 (score: 1), Yogurt: 2 (score: 2), Eggs: 3 (score: 3), Other Dairy Products: 4 (score: 4)</t>
+  </si>
+  <si>
+    <t>Fruit cocktail, fruit salad : 0 (score: 1), All other fruits: 1 (score: 2), Potatoes: 2 (score: 3), Cooked dried beans: 3 (score: 4), Salad greens: 4 (score: 5), All other vegetables: 5 (score: 6)</t>
+  </si>
+  <si>
+    <t>Candy: 0 (score: 1), Cookies, pie, cake, brownies: 1 (score: 2), Ice cream, sorbet, frozen yogurt: 2 (score: 3), Popcorn, crackers, chips, pretzels: 3 (score: 4), Other Snack Foods, Dessert Products: 4 (score: 5)</t>
+  </si>
+  <si>
+    <t>Cereal: 0 (score: 1), Rolls, English muffins, bagels: 1 (score: 2), All other bread: 2 (score: 3), Tortillas: 3 (score: 4), Doughnuts, Danish, sweet rolls, muffins, dessert breads, pop-tarts : 4 (score: 5), Pancakes, waffles, French toast: 5 (score: 6), Rice: 6 (score: 7), Pasta, spaghetti, noodles: 7 (score: 8)</t>
+  </si>
+  <si>
+    <t>Tobacco, cigarettes, e-cigarettes: 0 (score: 1), Cannabis, marijuana: 1 (score: 2), Other drugs: 2 (score: 3), Alcohol: 3 (score: 4), None of the above: 4 (score: 5)</t>
+  </si>
+  <si>
+    <t>Tobacco, cigarettes, e-cigarettes: 0 (score: 1), Cannabis, marijuana: 1 (score: 2), Other drugs: 2 (score: 3), None of the above: 3 (score: 4)</t>
+  </si>
+  <si>
+    <t>Cigarettes: 0 (score: 1), E-cigarettes/ Other Electronic Nicotine Device: 1 (score: 2), Other tobacco products (cigars, smokeless, hookah, other): 2 (score: 3)</t>
+  </si>
+  <si>
+    <t>1 cigarette: 0 (score: 1), 2 cigarettes: 1 (score: 2), 3 cigarettes: 2 (score: 3), 4 cigarettes: 3 (score: 4), 5 cigarettes: 4 (score: 5), 6-10 cigarettes: 5 (score: 6), 10-20 cigarettes: 6 (score: 7), Over 20 cigarettes: 7 (score: 8)</t>
+  </si>
+  <si>
+    <t>1 time: 0 (score: 1), 2 times: 1 (score: 2), 3 times: 2 (score: 3), 4 times: 3 (score: 4), 5 times: 4 (score: 5), 6-10 times: 5 (score: 6), 10-20 times: 6 (score: 7), Over 20 times: 7 (score: 8)</t>
+  </si>
+  <si>
+    <t>Bud, weed, or other dried leaf: 0 (score: 1), Concentrated cannabis (oils, vaping, resin, hash): 1 (score: 2), Edibles (gummies, beverages, chocolate, baked goods): 2 (score: 3)</t>
+  </si>
+  <si>
+    <t>Cocaine: 0 (score: 1), Tranquilizers (e.g., barbiturates): 1 (score: 2), Stimulants (e.g., speed, methamphetamine) : 2 (score: 3), Painkillers (e.g., Oxycontin) : 3 (score: 4), Heroin or Fentanyl: 4 (score: 5), Psychedelics (e.g., LSD): 5 (score: 6), Other drug (e.g., inhalants, nitrous) : 6 (score: 7)</t>
+  </si>
+  <si>
+    <t>Alone: 0 (score: 1), With other people: 1 (score: 2)</t>
+  </si>
+  <si>
+    <t>Headache: 0 (score: 1), Back/neck/shoulder: 1 (score: 2), Arms/hands: 2 (score: 3), Feet/legs: 3 (score: 4), Stomach/bowel: 4 (score: 5), Menstrual cramps (Females only): 5 (score: 6), Other Perineal (Females only) : 6 (score: 7)</t>
+  </si>
+  <si>
+    <t>Take prescribed medicine : 0 (score: 1), Take over the counter medicine : 1 (score: 2), Reduce or change activities: 2 (score: 3), Use relaxation, yoga or other techniques : 3 (score: 4), Rest or take a nap: 4 (score: 5), Other prevention strategy: 5 (score: 6), None of the above: 6 (score: 7)</t>
+  </si>
+  <si>
+    <t>Both sides of your head: 0 (score: 1), Left side only: 1 (score: 2), Right side only: 2 (score: 3), Moved from one side to another: 3 (score: 4)</t>
+  </si>
+  <si>
+    <t>Not at all: 0 (score: 1), Mildly: 1 (score: 2), Moderately: 2 (score: 3), Severely: 3 (score: 4)</t>
+  </si>
+  <si>
+    <t>Blurred or distorted vision: 0 (score: 1), Flashing lights, shapes: 1 (score: 2), Blind spots or missing parts: 2 (score: 3), None of the Above: 3 (score: 4)</t>
+  </si>
+  <si>
+    <t>Before headache pain: 0 (score: 1), After headache pain: 1 (score: 2)</t>
+  </si>
+  <si>
+    <t>Over-the-counter medications : 0 (score: 1), Prescription medications : 1 (score: 2), I did not take any medication for my headache: 2 (score: 3)</t>
+  </si>
+  <si>
+    <t>Allergies: 0 (score: 1), Asthma or breathing difficulties: 1 (score: 2), Gastrointestinal, bowel or stomach problems : 2 (score: 3), Muscle/joint pain: 3 (score: 4), Heart racing or pounding: 4 (score: 5), Feeling faint or dizzy: 6 (score: 6), Fever/Cold: 7 (score: 7), None of the above: 8 (score: 8)</t>
+  </si>
+  <si>
+    <t>Pain (Headache, muscle or joint pain, etc.) : 0 (score: 1), Allergies/cold: 1 (score: 2), Fever/Cold: 2 (score: 3), Sleep: 3 (score: 4), Other: 4 (score: 5)</t>
+  </si>
+  <si>
+    <t>Birth control: 0 (score: 1), Heart/blood pressure/cholesterol: 1 (score: 2), Thyroid/metabolic: 2 (score: 3), Sleep: 3 (score: 4), Anxiety/depression: 4 (score: 5), Attention/hyperactivity: 5 (score: 6), Asthma/allergies/breathing problems: 6 (score: 7), Arthritis, joint or back pain : 7 (score: 8), Other: 8 (score: 9)</t>
+  </si>
+  <si>
+    <t>Pain in your abdomen: 0 (score: 1), Diarrhea: 1 (score: 2), Nausea: 2 (score: 3), Vomiting: 3 (score: 4)</t>
+  </si>
+  <si>
+    <t>Yes: 0 (score: 1), No: 1 (score: 0)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3300,6 +3557,12 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3483,7 +3746,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3584,6 +3847,9 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3592,15 +3858,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -3629,6 +3886,21 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3968,34 +4240,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DC3F330-7399-DF41-9FB7-43E7ACD75EF2}">
-  <dimension ref="A1:H204"/>
+  <dimension ref="A1:I207"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.6640625" style="8" customWidth="1"/>
     <col min="2" max="2" width="33.33203125" style="8" customWidth="1"/>
     <col min="3" max="3" width="21" style="8" customWidth="1"/>
     <col min="4" max="5" width="26.6640625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="18" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.83203125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="23.83203125" style="8" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="8"/>
+    <col min="6" max="7" width="18" style="8" customWidth="1"/>
+    <col min="8" max="8" width="24.83203125" style="8" customWidth="1"/>
+    <col min="9" max="9" width="23.83203125" style="8" customWidth="1"/>
+    <col min="10" max="16384" width="10.83203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="42" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="35"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I1" s="36"/>
+    </row>
+    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -4014,26 +4287,30 @@
       <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="H2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="I2" s="15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="43" t="s">
-        <v>752</v>
-      </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="45"/>
-    </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="41" t="s">
+        <v>751</v>
+      </c>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="43"/>
+    </row>
+    <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>10</v>
       </c>
@@ -4052,14 +4329,17 @@
       <c r="F4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>10</v>
       </c>
@@ -4078,14 +4358,17 @@
       <c r="F5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>10</v>
       </c>
@@ -4104,558 +4387,623 @@
       <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>735</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="26" t="s">
+        <v>740</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>749</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="26" t="s">
+        <v>742</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>736</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="26" t="s">
+      <c r="C9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="26" t="s">
+        <v>745</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>737</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="26" t="s">
+        <v>743</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>738</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="26" t="s">
+        <v>744</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>739</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="26" t="s">
         <v>741</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="12" t="s">
+      <c r="I12" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>768</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>769</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>774</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>770</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="26" t="s">
+        <v>775</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" t="s">
+        <v>776</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>772</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="41" t="s">
         <v>750</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>743</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>737</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>746</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>738</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>744</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>739</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>745</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="12" t="s">
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="43"/>
+    </row>
+    <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>735</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="26" t="s">
         <v>740</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>742</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>769</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="26" t="s">
-        <v>774</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>770</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>775</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>771</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="26" t="s">
-        <v>776</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>772</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" t="s">
-        <v>777</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>773</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="26" t="s">
-        <v>778</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="43" t="s">
-        <v>751</v>
-      </c>
-      <c r="B18" s="44"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="45"/>
-    </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>736</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="26" t="s">
-        <v>741</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I19" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>10</v>
       </c>
       <c r="B20" s="12" t="s">
+        <v>753</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" t="s">
+        <v>760</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" t="s">
+        <v>761</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>754</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" t="s">
-        <v>761</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>753</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="C22" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" t="s">
+        <v>767</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>755</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" t="s">
         <v>762</v>
       </c>
-      <c r="H21" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>755</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" t="s">
-        <v>768</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="12" t="s">
+      <c r="I23" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>756</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="C24" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" t="s">
         <v>763</v>
       </c>
-      <c r="H23" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="12" t="s">
+      <c r="I24" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>757</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="C25" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" t="s">
         <v>764</v>
       </c>
-      <c r="H24" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="12" t="s">
+      <c r="I25" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>758</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="C26" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" t="s">
         <v>765</v>
       </c>
-      <c r="H25" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B26" s="12" t="s">
+      <c r="I26" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>759</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" t="s">
+      <c r="C27" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" t="s">
         <v>766</v>
       </c>
-      <c r="H26" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>760</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" t="s">
-        <v>767</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="46" t="s">
+      <c r="I27" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="48"/>
-    </row>
-    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="45"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="46"/>
+    </row>
+    <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>18</v>
       </c>
@@ -4672,12 +5020,15 @@
       <c r="F29" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H29" s="6"/>
-    </row>
-    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I29" s="6"/>
+    </row>
+    <row r="30" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>24</v>
       </c>
@@ -4694,14 +5045,17 @@
       <c r="F30" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="I30" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>24</v>
       </c>
@@ -4720,14 +5074,17 @@
       <c r="F31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="50" t="s">
+        <v>794</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H31" s="33" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I31" s="33" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>36</v>
       </c>
@@ -4744,14 +5101,17 @@
       <c r="F32" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="I32" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>36</v>
       </c>
@@ -4770,26 +5130,30 @@
       <c r="F33" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="51" t="s">
+        <v>794</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H33" s="33" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="37" t="s">
+      <c r="I33" s="33" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="35"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
       <c r="H34" s="36"/>
-    </row>
-    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I34" s="37"/>
+    </row>
+    <row r="35" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
         <v>46</v>
       </c>
@@ -4806,14 +5170,17 @@
       <c r="F35" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G35" s="17" t="s">
+      <c r="G35" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="H35" s="21" t="s">
+      <c r="I35" s="21" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
         <v>46</v>
       </c>
@@ -4832,14 +5199,17 @@
       <c r="F36" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="51" t="s">
+        <v>794</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H36" s="18" t="s">
+      <c r="I36" s="18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
         <v>46</v>
       </c>
@@ -4858,12 +5228,15 @@
       <c r="F37" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="51" t="s">
+        <v>794</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H37" s="6"/>
-    </row>
-    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I37" s="6"/>
+    </row>
+    <row r="38" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
         <v>46</v>
       </c>
@@ -4882,12 +5255,15 @@
       <c r="F38" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="51" t="s">
+        <v>794</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H38" s="6"/>
-    </row>
-    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I38" s="6"/>
+    </row>
+    <row r="39" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
         <v>46</v>
       </c>
@@ -4906,12 +5282,15 @@
       <c r="F39" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="50" t="s">
+        <v>795</v>
+      </c>
+      <c r="H39" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H39" s="6"/>
-    </row>
-    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I39" s="6"/>
+    </row>
+    <row r="40" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
         <v>46</v>
       </c>
@@ -4930,14 +5309,17 @@
       <c r="F40" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" s="50" t="s">
+        <v>796</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H40" s="18" t="s">
+      <c r="I40" s="18" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
         <v>46</v>
       </c>
@@ -4956,12 +5338,15 @@
       <c r="F41" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="50" t="s">
+        <v>794</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H41" s="6"/>
-    </row>
-    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I41" s="6"/>
+    </row>
+    <row r="42" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
         <v>46</v>
       </c>
@@ -4980,12 +5365,15 @@
       <c r="F42" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G42" s="50" t="s">
+        <v>794</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H42" s="6"/>
-    </row>
-    <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I42" s="6"/>
+    </row>
+    <row r="43" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>46</v>
       </c>
@@ -5004,12 +5392,15 @@
       <c r="F43" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="H43" s="6"/>
-    </row>
-    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I43" s="6"/>
+    </row>
+    <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>46</v>
       </c>
@@ -5028,12 +5419,15 @@
       <c r="F44" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="G44" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H44" s="6"/>
-    </row>
-    <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I44" s="6"/>
+    </row>
+    <row r="45" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>46</v>
       </c>
@@ -5052,12 +5446,15 @@
       <c r="F45" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="G45" s="50" t="s">
+        <v>798</v>
+      </c>
+      <c r="H45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H45" s="6"/>
-    </row>
-    <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I45" s="6"/>
+    </row>
+    <row r="46" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>46</v>
       </c>
@@ -5076,14 +5473,17 @@
       <c r="F46" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="G46" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H46" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H46" s="22" t="s">
+      <c r="I46" s="22" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>46</v>
       </c>
@@ -5102,24 +5502,28 @@
       <c r="F47" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" s="50" t="s">
+        <v>799</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H47" s="6"/>
-    </row>
-    <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="37" t="s">
+      <c r="I47" s="6"/>
+    </row>
+    <row r="48" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="B48" s="35"/>
-      <c r="C48" s="35"/>
-      <c r="D48" s="35"/>
-      <c r="E48" s="35"/>
-      <c r="F48" s="35"/>
-      <c r="G48" s="35"/>
+      <c r="B48" s="36"/>
+      <c r="C48" s="36"/>
+      <c r="D48" s="36"/>
+      <c r="E48" s="36"/>
+      <c r="F48" s="36"/>
+      <c r="G48" s="36"/>
       <c r="H48" s="36"/>
-    </row>
-    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I48" s="37"/>
+    </row>
+    <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>103</v>
       </c>
@@ -5133,15 +5537,20 @@
         <v>106</v>
       </c>
       <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="3" t="s">
+      <c r="F49" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="G49" s="51" t="s">
+        <v>800</v>
+      </c>
+      <c r="H49" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="H49" s="33" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I49" s="33" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>103</v>
       </c>
@@ -5158,12 +5567,15 @@
       <c r="F50" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G50" s="3" t="s">
+      <c r="G50" s="50" t="s">
+        <v>801</v>
+      </c>
+      <c r="H50" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="H50" s="3"/>
-    </row>
-    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I50" s="3"/>
+    </row>
+    <row r="51" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>103</v>
       </c>
@@ -5182,14 +5594,17 @@
       <c r="F51" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="G51" s="50" t="s">
+        <v>802</v>
+      </c>
+      <c r="H51" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H51" s="3" t="s">
+      <c r="I51" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>103</v>
       </c>
@@ -5208,14 +5623,17 @@
       <c r="F52" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="G52" s="50" t="s">
+        <v>803</v>
+      </c>
+      <c r="H52" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="H52" s="3" t="s">
+      <c r="I52" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>103</v>
       </c>
@@ -5232,12 +5650,15 @@
       <c r="F53" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="G53" s="50" t="s">
+        <v>804</v>
+      </c>
+      <c r="H53" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H53" s="23"/>
-    </row>
-    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I53" s="23"/>
+    </row>
+    <row r="54" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>103</v>
       </c>
@@ -5256,14 +5677,17 @@
       <c r="F54" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="G54" s="50" t="s">
+        <v>805</v>
+      </c>
+      <c r="H54" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H54" s="3" t="s">
+      <c r="I54" s="3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>103</v>
       </c>
@@ -5282,12 +5706,15 @@
       <c r="F55" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="G55" s="3" t="s">
+      <c r="G55" s="50" t="s">
+        <v>806</v>
+      </c>
+      <c r="H55" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="H55" s="3"/>
-    </row>
-    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I55" s="3"/>
+    </row>
+    <row r="56" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>103</v>
       </c>
@@ -5306,14 +5733,17 @@
       <c r="F56" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="G56" s="3" t="s">
+      <c r="G56" s="50" t="s">
+        <v>807</v>
+      </c>
+      <c r="H56" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="H56" s="3" t="s">
+      <c r="I56" s="3" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>103</v>
       </c>
@@ -5330,14 +5760,17 @@
       <c r="F57" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="G57" s="50" t="s">
+        <v>807</v>
+      </c>
+      <c r="H57" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="H57" s="3" t="s">
+      <c r="I57" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
         <v>103</v>
       </c>
@@ -5354,14 +5787,17 @@
       <c r="F58" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G58" s="50" t="s">
+        <v>808</v>
+      </c>
+      <c r="H58" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H58" s="3" t="s">
+      <c r="I58" s="3" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>103</v>
       </c>
@@ -5378,26 +5814,30 @@
       <c r="F59" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="G59" s="12" t="s">
+      <c r="G59" s="50" t="s">
+        <v>808</v>
+      </c>
+      <c r="H59" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="H59" s="3" t="s">
+      <c r="I59" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="38" t="s">
+    <row r="60" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="48" t="s">
         <v>158</v>
       </c>
-      <c r="B60" s="35"/>
-      <c r="C60" s="35"/>
-      <c r="D60" s="35"/>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="35"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="36"/>
+      <c r="D60" s="36"/>
+      <c r="E60" s="36"/>
+      <c r="F60" s="36"/>
+      <c r="G60" s="36"/>
       <c r="H60" s="36"/>
-    </row>
-    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I60" s="37"/>
+    </row>
+    <row r="61" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>103</v>
       </c>
@@ -5416,12 +5856,15 @@
       <c r="F61" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="G61" s="12" t="s">
+      <c r="G61" s="50" t="s">
+        <v>810</v>
+      </c>
+      <c r="H61" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="H61" s="6"/>
-    </row>
-    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I61" s="6"/>
+    </row>
+    <row r="62" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>103</v>
       </c>
@@ -5440,12 +5883,15 @@
       <c r="F62" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" s="50" t="s">
+        <v>811</v>
+      </c>
+      <c r="H62" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="H62" s="6"/>
-    </row>
-    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I62" s="6"/>
+    </row>
+    <row r="63" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>103</v>
       </c>
@@ -5455,3212 +5901,3693 @@
       <c r="C63" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D63" s="3"/>
+      <c r="D63" s="3" t="s">
+        <v>778</v>
+      </c>
       <c r="E63" s="3" t="s">
         <v>170</v>
       </c>
       <c r="F63" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="G63" s="50" t="s">
+        <v>815</v>
+      </c>
+      <c r="H63" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G63" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H63" s="6"/>
-    </row>
-    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I63" s="6"/>
+    </row>
+    <row r="64" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B64" s="27" t="s">
-        <v>173</v>
+      <c r="B64" s="29" t="s">
+        <v>780</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>174</v>
+        <v>783</v>
       </c>
       <c r="E64" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="F64" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F64" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H64" s="6"/>
-    </row>
-    <row r="65" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G64" s="50" t="s">
+        <v>816</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="I64" s="6"/>
+    </row>
+    <row r="65" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>103</v>
       </c>
       <c r="B65" s="29" t="s">
-        <v>178</v>
+        <v>781</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>179</v>
+        <v>785</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>180</v>
+        <v>784</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H65" s="6"/>
-    </row>
-    <row r="66" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>786</v>
+      </c>
+      <c r="G65" s="50" t="s">
+        <v>817</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="I65" s="6"/>
+    </row>
+    <row r="66" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B66" s="27" t="s">
-        <v>182</v>
+      <c r="B66" s="29" t="s">
+        <v>782</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>183</v>
+        <v>787</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="H66" s="18" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>788</v>
+      </c>
+      <c r="F66" s="4"/>
+      <c r="G66" s="53"/>
+      <c r="H66" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="I66" s="6"/>
+    </row>
+    <row r="67" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B67" s="29" t="s">
-        <v>187</v>
+      <c r="B67" s="27" t="s">
+        <v>172</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="H67" s="6"/>
-    </row>
-    <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+      <c r="G67" s="50" t="s">
+        <v>812</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I67" s="6"/>
+    </row>
+    <row r="68" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B68" s="27" t="s">
-        <v>192</v>
+      <c r="B68" s="29" t="s">
+        <v>177</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="H68" s="6"/>
-    </row>
-    <row r="69" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+      <c r="G68" s="50" t="s">
+        <v>812</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I68" s="6"/>
+    </row>
+    <row r="69" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>103</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="H69" s="6"/>
-    </row>
-    <row r="70" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+      <c r="G69" s="50" t="s">
+        <v>813</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I69" s="18" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B70" s="27" t="s">
+      <c r="B70" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G70" s="50" t="s">
+        <v>814</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="I70" s="6"/>
+    </row>
+    <row r="71" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B71" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G71" s="50" t="s">
+        <v>814</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="I71" s="6"/>
+    </row>
+    <row r="72" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B72" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G72" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="I72" s="6"/>
+    </row>
+    <row r="73" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B73" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C70" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D70" s="3" t="s">
+      <c r="E73" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="F73" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G73" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H73" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="F70" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="G70" s="3" t="s">
+      <c r="I73" s="6"/>
+    </row>
+    <row r="74" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="48" t="s">
         <v>204</v>
       </c>
-      <c r="H70" s="6"/>
-    </row>
-    <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="38" t="s">
+      <c r="B74" s="36"/>
+      <c r="C74" s="36"/>
+      <c r="D74" s="36"/>
+      <c r="E74" s="36"/>
+      <c r="F74" s="36"/>
+      <c r="G74" s="36"/>
+      <c r="H74" s="36"/>
+      <c r="I74" s="37"/>
+    </row>
+    <row r="75" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="B71" s="35"/>
-      <c r="C71" s="35"/>
-      <c r="D71" s="35"/>
-      <c r="E71" s="35"/>
-      <c r="F71" s="35"/>
-      <c r="G71" s="35"/>
-      <c r="H71" s="36"/>
-    </row>
-    <row r="72" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="6" t="s">
+      <c r="B75" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="B72" s="29" t="s">
+      <c r="C75" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E72" s="3"/>
-      <c r="F72" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="H72" s="6"/>
-    </row>
-    <row r="73" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B73" s="28" t="s">
-        <v>211</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E73" s="3"/>
-      <c r="F73" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="H73" s="6"/>
-    </row>
-    <row r="74" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B74" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E74" s="3"/>
-      <c r="F74" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="H74" s="6"/>
-    </row>
-    <row r="75" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B75" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="H75" s="6"/>
-    </row>
-    <row r="76" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="G75" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="I75" s="6"/>
+    </row>
+    <row r="76" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B76" s="29" t="s">
-        <v>223</v>
+        <v>205</v>
+      </c>
+      <c r="B76" s="28" t="s">
+        <v>210</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="H76" s="6"/>
-    </row>
-    <row r="77" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>212</v>
+      </c>
+      <c r="G76" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="I76" s="6"/>
+    </row>
+    <row r="77" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B77" s="29" t="s">
-        <v>227</v>
+        <v>205</v>
+      </c>
+      <c r="B77" s="27" t="s">
+        <v>214</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="H77" s="6"/>
-    </row>
-    <row r="78" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>216</v>
+      </c>
+      <c r="G77" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="I77" s="6"/>
+    </row>
+    <row r="78" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B78" s="29" t="s">
-        <v>231</v>
+        <v>205</v>
+      </c>
+      <c r="B78" s="31" t="s">
+        <v>218</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="H78" s="6"/>
-    </row>
-    <row r="79" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>220</v>
+      </c>
+      <c r="G78" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="I78" s="6"/>
+    </row>
+    <row r="79" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B79" s="29" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D79" s="6" t="s">
-        <v>236</v>
+      <c r="D79" s="3" t="s">
+        <v>223</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="H79" s="6"/>
-    </row>
-    <row r="80" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>224</v>
+      </c>
+      <c r="G79" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="I79" s="6"/>
+    </row>
+    <row r="80" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B80" s="29" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="H80" s="6"/>
-    </row>
-    <row r="81" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="39" t="s">
-        <v>243</v>
-      </c>
-      <c r="B81" s="35"/>
-      <c r="C81" s="35"/>
-      <c r="D81" s="35"/>
-      <c r="E81" s="35"/>
-      <c r="F81" s="35"/>
-      <c r="G81" s="35"/>
-      <c r="H81" s="36"/>
-    </row>
-    <row r="82" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+      <c r="G80" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="I80" s="6"/>
+    </row>
+    <row r="81" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B81" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E81" s="3"/>
+      <c r="F81" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="G81" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="I81" s="6"/>
+    </row>
+    <row r="82" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B82" s="29" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>245</v>
+      <c r="D82" s="6" t="s">
+        <v>235</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>247</v>
+        <v>236</v>
+      </c>
+      <c r="G82" s="50" t="s">
+        <v>797</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>237</v>
+      </c>
+      <c r="I82" s="6"/>
+    </row>
+    <row r="83" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B83" s="29" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="G83" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="I83" s="6"/>
+    </row>
+    <row r="84" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="49" t="s">
+        <v>242</v>
+      </c>
+      <c r="B84" s="36"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+      <c r="G84" s="36"/>
+      <c r="H84" s="36"/>
+      <c r="I84" s="37"/>
+    </row>
+    <row r="85" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B85" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E85" s="3"/>
+      <c r="F85" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="G85" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B86" s="29" t="s">
+        <v>248</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E86" s="3"/>
+      <c r="F86" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="G86" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H86" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="G83" s="3" t="s">
+      <c r="I86" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="H83" s="3" t="s">
+    </row>
+    <row r="87" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B87" s="29" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B84" s="29" t="s">
+      <c r="C87" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C84" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D84" s="3" t="s">
+      <c r="E87" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="E84" s="3" t="s">
+      <c r="F87" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="G87" s="50" t="s">
+        <v>818</v>
+      </c>
+      <c r="H87" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="G84" s="3" t="s">
+      <c r="I87" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="H84" s="3" t="s">
+    </row>
+    <row r="88" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B88" s="29" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B85" s="29" t="s">
+      <c r="C88" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C85" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D85" s="3" t="s">
+      <c r="E88" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="F88" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="E85" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="F85" s="4" t="s">
+      <c r="G88" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H88" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="G85" s="3" t="s">
+      <c r="I88" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="H85" s="3" t="s">
+    </row>
+    <row r="89" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B89" s="27" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B86" s="27" t="s">
+      <c r="C89" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C86" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D86" s="3" t="s">
+      <c r="E89" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="E86" s="3" t="s">
+      <c r="F89" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="F86" s="4" t="s">
+      <c r="G89" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H89" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="G86" s="3" t="s">
+      <c r="I89" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="H86" s="3" t="s">
+    </row>
+    <row r="90" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B90" s="27" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B87" s="27" t="s">
+      <c r="C90" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C87" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D87" s="3" t="s">
+      <c r="E90" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="G90" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H90" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="E87" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="G87" s="3" t="s">
+      <c r="I90" s="6"/>
+    </row>
+    <row r="91" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B91" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="H87" s="6"/>
-    </row>
-    <row r="88" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B88" s="27" t="s">
+      <c r="C91" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D91" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="C88" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D88" s="3" t="s">
+      <c r="E91" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="E88" s="3" t="s">
+      <c r="F91" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="F88" s="4" t="s">
+      <c r="G91" s="50" t="s">
+        <v>819</v>
+      </c>
+      <c r="H91" s="18" t="s">
         <v>277</v>
       </c>
-      <c r="G88" s="18" t="s">
+      <c r="I91" s="6"/>
+    </row>
+    <row r="92" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="35" t="s">
         <v>278</v>
       </c>
-      <c r="H88" s="6"/>
-    </row>
-    <row r="89" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="34" t="s">
+      <c r="B92" s="36"/>
+      <c r="C92" s="36"/>
+      <c r="D92" s="36"/>
+      <c r="E92" s="36"/>
+      <c r="F92" s="36"/>
+      <c r="G92" s="36"/>
+      <c r="H92" s="36"/>
+      <c r="I92" s="37"/>
+    </row>
+    <row r="93" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="B89" s="35"/>
-      <c r="C89" s="35"/>
-      <c r="D89" s="35"/>
-      <c r="E89" s="35"/>
-      <c r="F89" s="35"/>
-      <c r="G89" s="35"/>
-      <c r="H89" s="36"/>
-    </row>
-    <row r="90" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="6" t="s">
+      <c r="B93" s="29" t="s">
         <v>280</v>
       </c>
-      <c r="B90" s="29" t="s">
+      <c r="C93" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="C90" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D90" s="3" t="s">
+      <c r="E93" s="3"/>
+      <c r="F93" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="E90" s="3"/>
-      <c r="F90" s="4" t="s">
+      <c r="G93" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="H93" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="G90" s="3" t="s">
+      <c r="I93" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="H90" s="3" t="s">
+    </row>
+    <row r="94" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B94" s="27" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="B91" s="27" t="s">
+      <c r="C94" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D94" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="C91" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D91" s="4" t="s">
+      <c r="E94" s="4"/>
+      <c r="F94" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4" t="s">
+      <c r="G94" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H94" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="G91" s="3" t="s">
+      <c r="I94" s="6"/>
+    </row>
+    <row r="95" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B95" s="28" t="s">
         <v>289</v>
       </c>
-      <c r="H91" s="6"/>
-    </row>
-    <row r="92" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="B92" s="28" t="s">
+      <c r="C95" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D95" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C92" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D92" s="4" t="s">
+      <c r="E95" s="4"/>
+      <c r="F95" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4" t="s">
+      <c r="G95" s="50" t="s">
+        <v>820</v>
+      </c>
+      <c r="H95" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="G92" s="3" t="s">
+      <c r="I95" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="H92" s="3" t="s">
+    </row>
+    <row r="96" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B96" s="27" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="B93" s="27" t="s">
+      <c r="C96" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D96" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C93" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D93" s="3" t="s">
+      <c r="E96" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="E93" s="3" t="s">
+      <c r="F96" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="F93" s="4" t="s">
+      <c r="G96" s="50" t="s">
+        <v>821</v>
+      </c>
+      <c r="H96" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="G93" s="3" t="s">
+      <c r="I96" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="H93" s="3" t="s">
+    </row>
+    <row r="97" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B97" s="27" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="B94" s="27" t="s">
+      <c r="C97" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="C94" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D94" s="4" t="s">
+      <c r="E97" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="E94" s="4" t="s">
+      <c r="F97" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="F94" s="4" t="s">
+      <c r="G97" s="50" t="s">
+        <v>822</v>
+      </c>
+      <c r="H97" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="I97" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="H94" s="3" t="s">
+    </row>
+    <row r="98" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B98" s="27" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="B95" s="27" t="s">
+      <c r="C98" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="C95" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D95" s="4" t="s">
+      <c r="E98" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="E95" s="4" t="s">
+      <c r="F98" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F95" s="4" t="s">
+      <c r="G98" s="50" t="s">
+        <v>823</v>
+      </c>
+      <c r="H98" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="G95" s="3" t="s">
+      <c r="I98" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="H95" s="3" t="s">
+    </row>
+    <row r="99" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B99" s="27" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="B96" s="27" t="s">
+      <c r="C99" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D99" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="C96" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D96" s="4" t="s">
+      <c r="E99" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="E96" s="4" t="s">
+      <c r="F99" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="F96" s="4" t="s">
+      <c r="G99" s="50" t="s">
+        <v>824</v>
+      </c>
+      <c r="H99" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="I99" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H96" s="3" t="s">
+    </row>
+    <row r="100" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B100" s="27" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="B97" s="27" t="s">
+      <c r="C100" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="E100" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="C97" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="E97" s="4" t="s">
+      <c r="F100" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="F97" s="4" t="s">
+      <c r="G100" s="50" t="s">
+        <v>825</v>
+      </c>
+      <c r="H100" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="G97" s="3" t="s">
+      <c r="I100" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="H97" s="3" t="s">
+    </row>
+    <row r="101" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B101" s="27" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="B98" s="27" t="s">
+      <c r="C101" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D101" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="C98" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D98" s="4" t="s">
+      <c r="E101" s="4"/>
+      <c r="F101" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4" t="s">
+      <c r="G101" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H101" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="G98" s="3" t="s">
+      <c r="I101" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="H98" s="3" t="s">
+    </row>
+    <row r="102" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="47" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="37" t="s">
+      <c r="B102" s="36"/>
+      <c r="C102" s="36"/>
+      <c r="D102" s="36"/>
+      <c r="E102" s="36"/>
+      <c r="F102" s="36"/>
+      <c r="G102" s="36"/>
+      <c r="H102" s="36"/>
+      <c r="I102" s="37"/>
+    </row>
+    <row r="103" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="B99" s="35"/>
-      <c r="C99" s="35"/>
-      <c r="D99" s="35"/>
-      <c r="E99" s="35"/>
-      <c r="F99" s="35"/>
-      <c r="G99" s="35"/>
-      <c r="H99" s="36"/>
-    </row>
-    <row r="100" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="6" t="s">
+      <c r="B103" s="28" t="s">
         <v>330</v>
       </c>
-      <c r="B100" s="28" t="s">
+      <c r="C103" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D103" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="C100" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D100" s="4" t="s">
+      <c r="E103" s="4"/>
+      <c r="F103" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="E100" s="4"/>
-      <c r="F100" s="4" t="s">
+      <c r="G103" s="50" t="s">
+        <v>826</v>
+      </c>
+      <c r="H103" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G100" s="3" t="s">
+      <c r="I103" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="H100" s="3" t="s">
+    </row>
+    <row r="104" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B104" s="27" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="B101" s="27" t="s">
+      <c r="C104" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="C101" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D101" s="4" t="s">
+      <c r="E104" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="E101" s="4" t="s">
+      <c r="F104" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F101" s="4" t="s">
+      <c r="G104" s="50" t="s">
+        <v>827</v>
+      </c>
+      <c r="H104" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="I104" s="3"/>
+    </row>
+    <row r="105" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B105" s="27" t="s">
         <v>340</v>
       </c>
-      <c r="H101" s="3"/>
-    </row>
-    <row r="102" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="B102" s="27" t="s">
+      <c r="C105" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D105" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="C102" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D102" s="4" t="s">
+      <c r="E105" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="E102" s="4" t="s">
+      <c r="F105" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="F102" s="4" t="s">
+      <c r="G105" s="50" t="s">
+        <v>828</v>
+      </c>
+      <c r="H105" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="G102" s="3" t="s">
+      <c r="I105" s="6"/>
+    </row>
+    <row r="106" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B106" s="28" t="s">
         <v>345</v>
       </c>
-      <c r="H102" s="6"/>
-    </row>
-    <row r="103" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="B103" s="28" t="s">
+      <c r="C106" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D106" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="C103" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D103" s="4" t="s">
+      <c r="E106" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="F106" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="E103" s="4" t="s">
+      <c r="G106" s="50" t="s">
+        <v>796</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="I106" s="6"/>
+    </row>
+    <row r="107" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B107" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="G107" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="I107" s="6"/>
+    </row>
+    <row r="108" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B108" s="27" t="s">
+        <v>354</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="G108" s="50" t="s">
+        <v>796</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="I108" s="6"/>
+    </row>
+    <row r="109" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B109" s="28" t="s">
+        <v>358</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="G109" s="50" t="s">
+        <v>829</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="I109" s="6"/>
+    </row>
+    <row r="110" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B110" s="28" t="s">
+        <v>363</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="G110" s="50" t="s">
+        <v>829</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="I110" s="6"/>
+    </row>
+    <row r="111" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B111" s="28" t="s">
+        <v>367</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="G111" s="50" t="s">
+        <v>829</v>
+      </c>
+      <c r="H111" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="I111" s="6"/>
+    </row>
+    <row r="112" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="35" t="s">
+        <v>371</v>
+      </c>
+      <c r="B112" s="36"/>
+      <c r="C112" s="36"/>
+      <c r="D112" s="36"/>
+      <c r="E112" s="36"/>
+      <c r="F112" s="36"/>
+      <c r="G112" s="36"/>
+      <c r="H112" s="36"/>
+      <c r="I112" s="37"/>
+    </row>
+    <row r="113" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B113" s="27" t="s">
+        <v>373</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="E113" s="3"/>
+      <c r="F113" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="G113" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="I113" s="6"/>
+    </row>
+    <row r="114" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B114" s="28" t="s">
+        <v>377</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="E114" s="4"/>
+      <c r="F114" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="G114" s="50" t="s">
+        <v>830</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B115" s="27" t="s">
+        <v>382</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="G115" s="50" t="s">
+        <v>831</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I115" s="6"/>
+    </row>
+    <row r="116" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B116" s="29" t="s">
+        <v>387</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="G116" s="50" t="s">
+        <v>832</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I116" s="6"/>
+    </row>
+    <row r="117" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B117" s="28" t="s">
+        <v>392</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="G117" s="50" t="s">
+        <v>833</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B118" s="28" t="s">
+        <v>397</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="F118" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="F103" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="G103" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="H103" s="6"/>
-    </row>
-    <row r="104" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="B104" s="28" t="s">
-        <v>350</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D104" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="G104" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="H104" s="6"/>
-    </row>
-    <row r="105" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="B105" s="27" t="s">
-        <v>355</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="G105" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="H105" s="6"/>
-    </row>
-    <row r="106" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="B106" s="28" t="s">
-        <v>359</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="F106" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="G106" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="H106" s="6"/>
-    </row>
-    <row r="107" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="B107" s="28" t="s">
-        <v>364</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D107" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="F107" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="G107" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="H107" s="6"/>
-    </row>
-    <row r="108" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="B108" s="28" t="s">
-        <v>368</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D108" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="E108" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="F108" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="G108" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="H108" s="6"/>
-    </row>
-    <row r="109" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="34" t="s">
+      <c r="G118" s="50" t="s">
+        <v>828</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="I118" s="3"/>
+    </row>
+    <row r="119" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="B109" s="35"/>
-      <c r="C109" s="35"/>
-      <c r="D109" s="35"/>
-      <c r="E109" s="35"/>
-      <c r="F109" s="35"/>
-      <c r="G109" s="35"/>
-      <c r="H109" s="36"/>
-    </row>
-    <row r="110" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B110" s="27" t="s">
-        <v>374</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="E110" s="3"/>
-      <c r="F110" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="H110" s="6"/>
-    </row>
-    <row r="111" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B111" s="28" t="s">
-        <v>378</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="E111" s="4"/>
-      <c r="F111" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="G111" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="H111" s="3" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B112" s="27" t="s">
-        <v>383</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="E112" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="F112" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="G112" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="H112" s="6"/>
-    </row>
-    <row r="113" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B113" s="29" t="s">
-        <v>388</v>
-      </c>
-      <c r="C113" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="F113" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="G113" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="H113" s="6"/>
-    </row>
-    <row r="114" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B114" s="28" t="s">
-        <v>393</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="E114" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="F114" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="G114" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B115" s="28" t="s">
-        <v>398</v>
-      </c>
-      <c r="C115" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D115" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="E115" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="G115" s="3" t="s">
+      <c r="B119" s="27" t="s">
         <v>400</v>
       </c>
-      <c r="H115" s="3"/>
-    </row>
-    <row r="116" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B116" s="27" t="s">
+      <c r="C119" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D119" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="C116" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D116" s="4" t="s">
+      <c r="E119" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="E116" s="4" t="s">
+      <c r="F119" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="F116" s="4" t="s">
+      <c r="G119" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H119" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="G116" s="3" t="s">
+      <c r="I119" s="6"/>
+    </row>
+    <row r="120" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B120" s="28" t="s">
         <v>405</v>
       </c>
-      <c r="H116" s="6"/>
-    </row>
-    <row r="117" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B117" s="28" t="s">
+      <c r="C120" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D120" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="C117" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D117" s="4" t="s">
+      <c r="E120" s="4"/>
+      <c r="F120" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="E117" s="4"/>
-      <c r="F117" s="4" t="s">
+      <c r="G120" s="50" t="s">
+        <v>834</v>
+      </c>
+      <c r="H120" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G117" s="3" t="s">
+      <c r="I120" s="3"/>
+    </row>
+    <row r="121" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B121" s="28" t="s">
         <v>409</v>
       </c>
-      <c r="H117" s="3"/>
-    </row>
-    <row r="118" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B118" s="28" t="s">
+      <c r="C121" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D121" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="C118" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D118" s="4" t="s">
+      <c r="E121" s="4"/>
+      <c r="F121" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="E118" s="4"/>
-      <c r="F118" s="4" t="s">
+      <c r="G121" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H121" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="G118" s="3" t="s">
+      <c r="I121" s="6"/>
+    </row>
+    <row r="122" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B122" s="27" t="s">
         <v>413</v>
       </c>
-      <c r="H118" s="6"/>
-    </row>
-    <row r="119" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B119" s="27" t="s">
+      <c r="C122" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D122" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="C119" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D119" s="4" t="s">
+      <c r="E122" s="4"/>
+      <c r="F122" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="E119" s="4"/>
-      <c r="F119" s="4" t="s">
+      <c r="G122" s="50" t="s">
+        <v>835</v>
+      </c>
+      <c r="H122" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="G119" s="3" t="s">
+      <c r="I122" s="6"/>
+    </row>
+    <row r="123" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B123" s="29" t="s">
         <v>417</v>
       </c>
-      <c r="H119" s="6"/>
-    </row>
-    <row r="120" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B120" s="29" t="s">
+      <c r="C123" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D123" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="C120" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D120" s="3" t="s">
+      <c r="E123" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="E120" s="4" t="s">
+      <c r="F123" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="F120" s="4" t="s">
+      <c r="G123" s="50" t="s">
+        <v>836</v>
+      </c>
+      <c r="H123" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="G120" s="3" t="s">
+      <c r="I123" s="6"/>
+    </row>
+    <row r="124" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B124" s="29" t="s">
         <v>422</v>
       </c>
-      <c r="H120" s="6"/>
-    </row>
-    <row r="121" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B121" s="29" t="s">
+      <c r="C124" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D124" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="C121" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D121" s="3" t="s">
+      <c r="E124" s="3"/>
+      <c r="F124" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G124" s="51" t="s">
+        <v>828</v>
+      </c>
+      <c r="H124" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="E121" s="3"/>
-      <c r="F121" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="G121" s="3" t="s">
+      <c r="I124" s="6"/>
+    </row>
+    <row r="125" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="35" t="s">
         <v>425</v>
       </c>
-      <c r="H121" s="6"/>
-    </row>
-    <row r="122" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="34" t="s">
+      <c r="B125" s="36"/>
+      <c r="C125" s="36"/>
+      <c r="D125" s="36"/>
+      <c r="E125" s="36"/>
+      <c r="F125" s="36"/>
+      <c r="G125" s="36"/>
+      <c r="H125" s="36"/>
+      <c r="I125" s="37"/>
+    </row>
+    <row r="126" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="B122" s="35"/>
-      <c r="C122" s="35"/>
-      <c r="D122" s="35"/>
-      <c r="E122" s="35"/>
-      <c r="F122" s="35"/>
-      <c r="G122" s="35"/>
-      <c r="H122" s="36"/>
-    </row>
-    <row r="123" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="6" t="s">
+      <c r="B126" s="29" t="s">
         <v>427</v>
       </c>
-      <c r="B123" s="29" t="s">
+      <c r="C126" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="C123" s="6" t="s">
+      <c r="D126" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="D123" s="3" t="s">
+      <c r="E126" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="E123" s="3" t="s">
+      <c r="F126" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="F123" s="4" t="s">
+      <c r="G126" s="50" t="s">
+        <v>837</v>
+      </c>
+      <c r="H126" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="G123" s="3" t="s">
+      <c r="I126" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="H123" s="3" t="s">
+    </row>
+    <row r="127" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B127" s="27" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="124" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="B124" s="27" t="s">
+      <c r="C127" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D127" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="C124" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D124" s="3" t="s">
+      <c r="E127" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="E124" s="3" t="s">
+      <c r="F127" s="7" t="s">
         <v>437</v>
       </c>
-      <c r="F124" s="7" t="s">
+      <c r="G127" s="50" t="s">
+        <v>838</v>
+      </c>
+      <c r="H127" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="G124" s="3" t="s">
+      <c r="I127" s="6"/>
+    </row>
+    <row r="128" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B128" s="27" t="s">
         <v>439</v>
       </c>
-      <c r="H124" s="6"/>
-    </row>
-    <row r="125" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="B125" s="27" t="s">
+      <c r="C128" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D128" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="C125" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D125" s="3" t="s">
+      <c r="E128" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F128" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="E125" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="F125" s="7" t="s">
+      <c r="G128" s="50" t="s">
+        <v>839</v>
+      </c>
+      <c r="H128" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="G125" s="3" t="s">
+      <c r="I128" s="6"/>
+    </row>
+    <row r="129" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B129" s="27" t="s">
         <v>443</v>
       </c>
-      <c r="H125" s="6"/>
-    </row>
-    <row r="126" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="B126" s="27" t="s">
+      <c r="C129" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D129" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="C126" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D126" s="3" t="s">
+      <c r="E129" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F129" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="E126" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="F126" s="7" t="s">
+      <c r="G129" s="50" t="s">
+        <v>840</v>
+      </c>
+      <c r="H129" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="G126" s="3" t="s">
+      <c r="I129" s="6"/>
+    </row>
+    <row r="130" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B130" s="27" t="s">
         <v>447</v>
       </c>
-      <c r="H126" s="6"/>
-    </row>
-    <row r="127" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="B127" s="27" t="s">
+      <c r="C130" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D130" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="C127" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D127" s="3" t="s">
+      <c r="E130" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F130" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="E127" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="F127" s="7" t="s">
+      <c r="G130" s="50" t="s">
+        <v>841</v>
+      </c>
+      <c r="H130" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="G127" s="3" t="s">
+      <c r="I130" s="6"/>
+    </row>
+    <row r="131" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B131" s="27" t="s">
         <v>451</v>
       </c>
-      <c r="H127" s="6"/>
-    </row>
-    <row r="128" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="B128" s="27" t="s">
+      <c r="C131" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D131" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="C128" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D128" s="3" t="s">
+      <c r="E131" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F131" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="E128" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="F128" s="4" t="s">
+      <c r="G131" s="50" t="s">
+        <v>842</v>
+      </c>
+      <c r="H131" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="G128" s="3" t="s">
+      <c r="I131" s="6"/>
+    </row>
+    <row r="132" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="35" t="s">
         <v>455</v>
       </c>
-      <c r="H128" s="6"/>
-    </row>
-    <row r="129" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="34" t="s">
+      <c r="B132" s="36"/>
+      <c r="C132" s="36"/>
+      <c r="D132" s="36"/>
+      <c r="E132" s="36"/>
+      <c r="F132" s="36"/>
+      <c r="G132" s="36"/>
+      <c r="H132" s="36"/>
+      <c r="I132" s="37"/>
+    </row>
+    <row r="133" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="B129" s="35"/>
-      <c r="C129" s="35"/>
-      <c r="D129" s="35"/>
-      <c r="E129" s="35"/>
-      <c r="F129" s="35"/>
-      <c r="G129" s="35"/>
-      <c r="H129" s="36"/>
-    </row>
-    <row r="130" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="6" t="s">
+      <c r="B133" s="28" t="s">
         <v>457</v>
       </c>
-      <c r="B130" s="28" t="s">
+      <c r="C133" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D133" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="C130" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D130" s="7" t="s">
+      <c r="E133" s="11"/>
+      <c r="F133" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="E130" s="11"/>
-      <c r="F130" s="4" t="s">
+      <c r="G133" s="50" t="s">
+        <v>843</v>
+      </c>
+      <c r="H133" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="G130" s="3" t="s">
+      <c r="I133" s="24"/>
+    </row>
+    <row r="134" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="B134" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="H130" s="24"/>
-    </row>
-    <row r="131" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="B131" s="28" t="s">
+      <c r="C134" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D134" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="C131" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D131" s="7" t="s">
+      <c r="E134" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="E131" s="7" t="s">
+      <c r="F134" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="F131" s="7" t="s">
+      <c r="G134" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H134" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="G131" s="3" t="s">
+      <c r="I134" s="25"/>
+    </row>
+    <row r="135" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="B135" s="28" t="s">
         <v>466</v>
       </c>
-      <c r="H131" s="25"/>
-    </row>
-    <row r="132" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="B132" s="28" t="s">
+      <c r="C135" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D135" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="C132" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D132" s="7" t="s">
+      <c r="E135" s="7" t="s">
         <v>468</v>
       </c>
-      <c r="E132" s="7" t="s">
+      <c r="F135" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="G135" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H135" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="F132" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="G132" s="3" t="s">
+      <c r="I135" s="6"/>
+    </row>
+    <row r="136" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="B136" s="28" t="s">
         <v>470</v>
       </c>
-      <c r="H132" s="6"/>
-    </row>
-    <row r="133" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="B133" s="28" t="s">
+      <c r="C136" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D136" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="C133" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D133" s="7" t="s">
+      <c r="E136" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="E133" s="7" t="s">
+      <c r="F136" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="G136" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H136" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="F133" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="G133" s="3" t="s">
+      <c r="I136" s="6"/>
+    </row>
+    <row r="137" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="B137" s="28" t="s">
         <v>474</v>
       </c>
-      <c r="H133" s="6"/>
-    </row>
-    <row r="134" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="B134" s="28" t="s">
+      <c r="C137" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D137" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="C134" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D134" s="7" t="s">
+      <c r="E137" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="E134" s="7" t="s">
+      <c r="F137" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="G137" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H137" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="F134" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="G134" s="3" t="s">
+      <c r="I137" s="6"/>
+    </row>
+    <row r="138" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="B138" s="29" t="s">
         <v>478</v>
       </c>
-      <c r="H134" s="6"/>
-    </row>
-    <row r="135" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="B135" s="29" t="s">
+      <c r="C138" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D138" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="C135" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D135" s="3" t="s">
+      <c r="E138" s="3"/>
+      <c r="F138" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="E135" s="3"/>
-      <c r="F135" s="4" t="s">
+      <c r="G138" s="50" t="s">
+        <v>844</v>
+      </c>
+      <c r="H138" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="G135" s="3" t="s">
+      <c r="I138" s="6"/>
+    </row>
+    <row r="139" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="H135" s="6"/>
-    </row>
-    <row r="136" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="6" t="s">
+      <c r="B139" s="27" t="s">
         <v>483</v>
       </c>
-      <c r="B136" s="27" t="s">
+      <c r="C139" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D139" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="C136" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D136" s="3" t="s">
+      <c r="E139" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E136" s="3" t="s">
+      <c r="F139" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="F136" s="4" t="s">
+      <c r="G139" s="50" t="s">
+        <v>845</v>
+      </c>
+      <c r="H139" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="G136" s="3" t="s">
+      <c r="I139" s="6"/>
+    </row>
+    <row r="140" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B140" s="29" t="s">
         <v>488</v>
       </c>
-      <c r="H136" s="6"/>
-    </row>
-    <row r="137" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="B137" s="29" t="s">
+      <c r="C140" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D140" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="C137" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D137" s="3" t="s">
+      <c r="E140" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="E137" s="3" t="s">
+      <c r="F140" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="F137" s="4" t="s">
+      <c r="G140" s="50" t="s">
+        <v>846</v>
+      </c>
+      <c r="H140" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="G137" s="3" t="s">
+      <c r="I140" s="6"/>
+    </row>
+    <row r="141" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B141" s="27" t="s">
         <v>493</v>
       </c>
-      <c r="H137" s="6"/>
-    </row>
-    <row r="138" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="B138" s="27" t="s">
+      <c r="C141" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D141" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="C138" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D138" s="4" t="s">
+      <c r="E141" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G141" s="50" t="s">
+        <v>828</v>
+      </c>
+      <c r="H141" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="E138" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="F138" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="G138" s="3" t="s">
+      <c r="I141" s="6"/>
+    </row>
+    <row r="142" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B142" s="27" t="s">
         <v>496</v>
       </c>
-      <c r="H138" s="6"/>
-    </row>
-    <row r="139" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="B139" s="27" t="s">
+      <c r="C142" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D142" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="C139" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D139" s="4" t="s">
+      <c r="E142" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="E139" s="3" t="s">
+      <c r="F142" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="F139" s="4" t="s">
+      <c r="G142" s="50" t="s">
+        <v>847</v>
+      </c>
+      <c r="H142" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="G139" s="3" t="s">
+      <c r="I142" s="6"/>
+    </row>
+    <row r="143" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B143" s="27" t="s">
         <v>501</v>
       </c>
-      <c r="H139" s="6"/>
-    </row>
-    <row r="140" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="B140" s="27" t="s">
+      <c r="C143" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D143" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="C140" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D140" s="4" t="s">
+      <c r="E143" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G143" s="50" t="s">
+        <v>828</v>
+      </c>
+      <c r="H143" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="E140" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="F140" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="G140" s="3" t="s">
+      <c r="I143" s="6"/>
+    </row>
+    <row r="144" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B144" s="27" t="s">
         <v>504</v>
       </c>
-      <c r="H140" s="6"/>
-    </row>
-    <row r="141" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="B141" s="27" t="s">
+      <c r="C144" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D144" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="C141" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D141" s="4" t="s">
+      <c r="E144" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="E141" s="3" t="s">
+      <c r="F144" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="F141" s="4" t="s">
+      <c r="G144" s="50" t="s">
+        <v>847</v>
+      </c>
+      <c r="H144" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="G141" s="3" t="s">
+      <c r="I144" s="6"/>
+    </row>
+    <row r="145" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B145" s="27" t="s">
         <v>509</v>
       </c>
-      <c r="H141" s="6"/>
-    </row>
-    <row r="142" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="B142" s="27" t="s">
+      <c r="C145" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D145" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="C142" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D142" s="4" t="s">
+      <c r="E145" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G145" s="51" t="s">
+        <v>828</v>
+      </c>
+      <c r="H145" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="E142" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="F142" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="G142" s="3" t="s">
+      <c r="I145" s="6"/>
+    </row>
+    <row r="146" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B146" s="27" t="s">
         <v>512</v>
       </c>
-      <c r="H142" s="6"/>
-    </row>
-    <row r="143" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="B143" s="27" t="s">
+      <c r="C146" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D146" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="C143" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D143" s="4" t="s">
+      <c r="E146" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="E143" s="3" t="s">
+      <c r="F146" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="F143" s="4" t="s">
+      <c r="G146" s="50" t="s">
+        <v>848</v>
+      </c>
+      <c r="H146" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="G143" s="3" t="s">
+      <c r="I146" s="6"/>
+    </row>
+    <row r="147" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B147" s="27" t="s">
         <v>517</v>
       </c>
-      <c r="H143" s="6"/>
-    </row>
-    <row r="144" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="B144" s="27" t="s">
+      <c r="C147" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D147" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="C144" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D144" s="4" t="s">
+      <c r="E147" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G147" s="50" t="s">
+        <v>828</v>
+      </c>
+      <c r="H147" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="E144" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="F144" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="G144" s="3" t="s">
+      <c r="I147" s="6"/>
+    </row>
+    <row r="148" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B148" s="27" t="s">
         <v>520</v>
       </c>
-      <c r="H144" s="6"/>
-    </row>
-    <row r="145" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="B145" s="27" t="s">
+      <c r="C148" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D148" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="C145" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D145" s="4" t="s">
+      <c r="E148" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="F148" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="E145" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="F145" s="4" t="s">
+      <c r="G148" s="50" t="s">
+        <v>847</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="I148" s="6"/>
+    </row>
+    <row r="149" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B149" s="27" t="s">
         <v>523</v>
       </c>
-      <c r="G145" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="H145" s="6"/>
-    </row>
-    <row r="146" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="B146" s="27" t="s">
+      <c r="C149" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D149" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="C146" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D146" s="4" t="s">
+      <c r="E149" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="F149" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="E146" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="F146" s="4" t="s">
+      <c r="G149" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H149" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="G146" s="3" t="s">
+      <c r="I149" s="6"/>
+    </row>
+    <row r="150" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B150" s="27" t="s">
         <v>527</v>
       </c>
-      <c r="H146" s="6"/>
-    </row>
-    <row r="147" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="B147" s="27" t="s">
+      <c r="C150" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D150" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="C147" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D147" s="4" t="s">
+      <c r="E150" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="E147" s="4" t="s">
+      <c r="F150" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="F147" s="4" t="s">
+      <c r="G150" s="50" t="s">
+        <v>849</v>
+      </c>
+      <c r="H150" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="G147" s="3" t="s">
+      <c r="I150" s="3"/>
+    </row>
+    <row r="151" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B151" s="27" t="s">
         <v>532</v>
       </c>
-      <c r="H147" s="3"/>
-    </row>
-    <row r="148" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="B148" s="27" t="s">
+      <c r="C151" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D151" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="C148" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D148" s="4" t="s">
+      <c r="E151" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="E148" s="4" t="s">
+      <c r="F151" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="F148" s="4" t="s">
+      <c r="G151" s="51" t="s">
+        <v>535</v>
+      </c>
+      <c r="H151" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="G148" s="3" t="s">
+      <c r="I151" s="3"/>
+    </row>
+    <row r="152" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B152" s="27" t="s">
         <v>537</v>
       </c>
-      <c r="H148" s="3"/>
-    </row>
-    <row r="149" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="B149" s="27" t="s">
+      <c r="C152" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D152" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="C149" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D149" s="4" t="s">
+      <c r="E152" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G152" s="51" t="s">
+        <v>828</v>
+      </c>
+      <c r="H152" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="E149" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="F149" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="G149" s="3" t="s">
+      <c r="I152" s="6"/>
+    </row>
+    <row r="153" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B153" s="27" t="s">
         <v>540</v>
       </c>
-      <c r="H149" s="6"/>
-    </row>
-    <row r="150" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="B150" s="27" t="s">
+      <c r="C153" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="G153" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="I153" s="6"/>
+    </row>
+    <row r="154" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B154" s="27" t="s">
         <v>541</v>
       </c>
-      <c r="C150" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D150" s="4" t="s">
-        <v>525</v>
-      </c>
-      <c r="E150" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="F150" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="G150" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="H150" s="6"/>
-    </row>
-    <row r="151" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="B151" s="27" t="s">
+      <c r="C154" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D154" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C151" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D151" s="4" t="s">
+      <c r="E154" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="E151" s="4" t="s">
+      <c r="F154" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="F151" s="4" t="s">
+      <c r="G154" s="50" t="s">
+        <v>850</v>
+      </c>
+      <c r="H154" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="G151" s="3" t="s">
+      <c r="I154" s="6"/>
+    </row>
+    <row r="155" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="47" t="s">
         <v>546</v>
       </c>
-      <c r="H151" s="6"/>
-    </row>
-    <row r="152" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="37" t="s">
+      <c r="B155" s="36"/>
+      <c r="C155" s="36"/>
+      <c r="D155" s="36"/>
+      <c r="E155" s="36"/>
+      <c r="F155" s="36"/>
+      <c r="G155" s="36"/>
+      <c r="H155" s="36"/>
+      <c r="I155" s="37"/>
+    </row>
+    <row r="156" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="B152" s="35"/>
-      <c r="C152" s="35"/>
-      <c r="D152" s="35"/>
-      <c r="E152" s="35"/>
-      <c r="F152" s="35"/>
-      <c r="G152" s="35"/>
-      <c r="H152" s="36"/>
-    </row>
-    <row r="153" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="6" t="s">
+      <c r="B156" s="29" t="s">
         <v>548</v>
       </c>
-      <c r="B153" s="29" t="s">
+      <c r="C156" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D156" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="C153" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D153" s="3" t="s">
+      <c r="E156" s="3"/>
+      <c r="F156" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="E153" s="3"/>
-      <c r="F153" s="4" t="s">
+      <c r="G156" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H156" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="G153" s="3" t="s">
+      <c r="I156" s="6"/>
+    </row>
+    <row r="157" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B157" s="28" t="s">
         <v>552</v>
       </c>
-      <c r="H153" s="6"/>
-    </row>
-    <row r="154" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B154" s="28" t="s">
+      <c r="C157" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D157" s="4" t="s">
         <v>553</v>
       </c>
-      <c r="C154" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D154" s="4" t="s">
+      <c r="E157" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="E154" s="4" t="s">
+      <c r="F157" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="F154" s="4" t="s">
+      <c r="G157" s="50" t="s">
+        <v>851</v>
+      </c>
+      <c r="H157" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="G154" s="3" t="s">
+      <c r="I157" s="3"/>
+    </row>
+    <row r="158" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B158" s="29" t="s">
         <v>557</v>
       </c>
-      <c r="H154" s="3"/>
-    </row>
-    <row r="155" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B155" s="29" t="s">
+      <c r="C158" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D158" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="C155" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D155" s="3" t="s">
+      <c r="E158" s="3"/>
+      <c r="F158" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="E155" s="3"/>
-      <c r="F155" s="4" t="s">
+      <c r="G158" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H158" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="G155" s="3" t="s">
+      <c r="I158" s="6"/>
+    </row>
+    <row r="159" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B159" s="28" t="s">
         <v>561</v>
       </c>
-      <c r="H155" s="6"/>
-    </row>
-    <row r="156" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B156" s="28" t="s">
+      <c r="C159" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D159" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="C156" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D156" s="4" t="s">
+      <c r="E159" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="E156" s="4" t="s">
+      <c r="F159" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="G159" s="50" t="s">
+        <v>851</v>
+      </c>
+      <c r="H159" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="F156" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="G156" s="3" t="s">
+      <c r="I159" s="3"/>
+    </row>
+    <row r="160" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B160" s="28" t="s">
         <v>565</v>
       </c>
-      <c r="H156" s="3"/>
-    </row>
-    <row r="157" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B157" s="28" t="s">
+      <c r="C160" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D160" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="C157" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D157" s="4" t="s">
+      <c r="E160" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="E157" s="4" t="s">
+      <c r="F160" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="F157" s="4" t="s">
+      <c r="G160" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H160" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="G157" s="3" t="s">
+      <c r="I160" s="6"/>
+    </row>
+    <row r="161" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="35" t="s">
         <v>570</v>
       </c>
-      <c r="H157" s="6"/>
-    </row>
-    <row r="158" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="34" t="s">
+      <c r="B161" s="36"/>
+      <c r="C161" s="36"/>
+      <c r="D161" s="36"/>
+      <c r="E161" s="36"/>
+      <c r="F161" s="36"/>
+      <c r="G161" s="36"/>
+      <c r="H161" s="36"/>
+      <c r="I161" s="37"/>
+    </row>
+    <row r="162" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B162" s="29" t="s">
         <v>571</v>
       </c>
-      <c r="B158" s="35"/>
-      <c r="C158" s="35"/>
-      <c r="D158" s="35"/>
-      <c r="E158" s="35"/>
-      <c r="F158" s="35"/>
-      <c r="G158" s="35"/>
-      <c r="H158" s="36"/>
-    </row>
-    <row r="159" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B159" s="29" t="s">
+      <c r="C162" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D162" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="C159" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D159" s="3" t="s">
+      <c r="E162" s="3"/>
+      <c r="F162" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="E159" s="3"/>
-      <c r="F159" s="4" t="s">
+      <c r="G162" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H162" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="G159" s="3" t="s">
+      <c r="I162" s="6"/>
+    </row>
+    <row r="163" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B163" s="29" t="s">
         <v>575</v>
       </c>
-      <c r="H159" s="6"/>
-    </row>
-    <row r="160" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B160" s="29" t="s">
+      <c r="C163" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D163" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="C160" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D160" s="3" t="s">
+      <c r="E163" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="E160" s="3" t="s">
+      <c r="F163" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="F160" s="4" t="s">
+      <c r="G163" s="50" t="s">
+        <v>852</v>
+      </c>
+      <c r="H163" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="G160" s="3" t="s">
+      <c r="I163" s="6"/>
+    </row>
+    <row r="164" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B164" s="29" t="s">
         <v>580</v>
       </c>
-      <c r="H160" s="6"/>
-    </row>
-    <row r="161" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B161" s="29" t="s">
+      <c r="C164" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D164" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="C161" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D161" s="3" t="s">
+      <c r="E164" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="E161" s="3" t="s">
+      <c r="F164" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="G164" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H164" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="F161" s="4" t="s">
-        <v>574</v>
-      </c>
-      <c r="G161" s="3" t="s">
+      <c r="I164" s="20"/>
+    </row>
+    <row r="165" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B165" s="29" t="s">
         <v>584</v>
       </c>
-      <c r="H161" s="20"/>
-    </row>
-    <row r="162" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B162" s="29" t="s">
+      <c r="C165" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D165" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="C162" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D162" s="3" t="s">
+      <c r="E165" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="E162" s="3" t="s">
+      <c r="F165" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G165" s="51" t="s">
+        <v>828</v>
+      </c>
+      <c r="H165" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="F162" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="G162" s="3" t="s">
+      <c r="I165" s="20"/>
+    </row>
+    <row r="166" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B166" s="29" t="s">
         <v>588</v>
       </c>
-      <c r="H162" s="20"/>
-    </row>
-    <row r="163" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B163" s="29" t="s">
+      <c r="C166" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D166" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="C163" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D163" s="3" t="s">
+      <c r="E166" s="3"/>
+      <c r="F166" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="G166" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H166" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="E163" s="3"/>
-      <c r="F163" s="4" t="s">
-        <v>574</v>
-      </c>
-      <c r="G163" s="3" t="s">
+      <c r="I166" s="20"/>
+    </row>
+    <row r="167" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B167" s="29" t="s">
         <v>591</v>
       </c>
-      <c r="H163" s="20"/>
-    </row>
-    <row r="164" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B164" s="29" t="s">
+      <c r="C167" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D167" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="C164" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D164" s="3" t="s">
+      <c r="E167" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="E164" s="3" t="s">
+      <c r="F167" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G167" s="51" t="s">
+        <v>828</v>
+      </c>
+      <c r="H167" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="F164" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="G164" s="3" t="s">
+      <c r="I167" s="20"/>
+    </row>
+    <row r="168" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B168" s="29" t="s">
         <v>595</v>
       </c>
-      <c r="H164" s="20"/>
-    </row>
-    <row r="165" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B165" s="29" t="s">
+      <c r="C168" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D168" s="3" t="s">
         <v>596</v>
-      </c>
-      <c r="C165" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D165" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="E165" s="3"/>
-      <c r="F165" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="G165" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="H165" s="6"/>
-    </row>
-    <row r="166" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B166" s="29" t="s">
-        <v>600</v>
-      </c>
-      <c r="C166" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D166" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="E166" s="4"/>
-      <c r="F166" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="G166" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="H166" s="6"/>
-    </row>
-    <row r="167" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B167" s="29" t="s">
-        <v>604</v>
-      </c>
-      <c r="C167" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D167" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="E167" s="3"/>
-      <c r="F167" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="G167" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="H167" s="6"/>
-    </row>
-    <row r="168" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B168" s="29" t="s">
-        <v>607</v>
-      </c>
-      <c r="C168" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D168" s="3" t="s">
-        <v>608</v>
       </c>
       <c r="E168" s="3"/>
       <c r="F168" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="G168" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="H168" s="6"/>
-    </row>
-    <row r="169" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>597</v>
+      </c>
+      <c r="G168" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H168" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="I168" s="6"/>
+    </row>
+    <row r="169" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B169" s="28" t="s">
-        <v>610</v>
+        <v>547</v>
+      </c>
+      <c r="B169" s="29" t="s">
+        <v>599</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="E169" s="4"/>
       <c r="F169" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="G169" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="H169" s="6"/>
-    </row>
-    <row r="170" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>601</v>
+      </c>
+      <c r="G169" s="50" t="s">
+        <v>853</v>
+      </c>
+      <c r="H169" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="I169" s="6"/>
+    </row>
+    <row r="170" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B170" s="28" t="s">
-        <v>614</v>
+        <v>547</v>
+      </c>
+      <c r="B170" s="29" t="s">
+        <v>603</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D170" s="4" t="s">
-        <v>615</v>
-      </c>
-      <c r="E170" s="4"/>
+      <c r="D170" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="E170" s="3"/>
       <c r="F170" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="G170" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="H170" s="6"/>
-    </row>
-    <row r="171" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+      <c r="G170" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H170" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="I170" s="6"/>
+    </row>
+    <row r="171" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B171" s="27" t="s">
-        <v>617</v>
+        <v>547</v>
+      </c>
+      <c r="B171" s="29" t="s">
+        <v>606</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D171" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="E171" s="4"/>
+      <c r="D171" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="E171" s="3"/>
       <c r="F171" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="G171" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="H171" s="6"/>
-    </row>
-    <row r="172" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+      <c r="G171" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H171" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="I171" s="6"/>
+    </row>
+    <row r="172" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B172" s="28" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="E172" s="4"/>
       <c r="F172" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="G172" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="H172" s="6"/>
-    </row>
-    <row r="173" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>611</v>
+      </c>
+      <c r="G172" s="50" t="s">
+        <v>854</v>
+      </c>
+      <c r="H172" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="I172" s="6"/>
+    </row>
+    <row r="173" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B173" s="28" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="E173" s="4"/>
       <c r="F173" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="G173" s="3" t="s">
-        <v>626</v>
-      </c>
-      <c r="H173" s="6"/>
-    </row>
-    <row r="174" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>611</v>
+      </c>
+      <c r="G173" s="50" t="s">
+        <v>854</v>
+      </c>
+      <c r="H173" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="I173" s="6"/>
+    </row>
+    <row r="174" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B174" s="28" t="s">
-        <v>627</v>
+        <v>547</v>
+      </c>
+      <c r="B174" s="27" t="s">
+        <v>616</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="E174" s="4"/>
       <c r="F174" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="G174" s="3" t="s">
-        <v>629</v>
-      </c>
-      <c r="H174" s="6"/>
-    </row>
-    <row r="175" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>611</v>
+      </c>
+      <c r="G174" s="50" t="s">
+        <v>854</v>
+      </c>
+      <c r="H174" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="I174" s="6"/>
+    </row>
+    <row r="175" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B175" s="28" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="E175" s="4"/>
       <c r="F175" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="G175" s="50" t="s">
+        <v>854</v>
+      </c>
+      <c r="H175" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="I175" s="6"/>
+    </row>
+    <row r="176" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B176" s="28" t="s">
+        <v>623</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="E176" s="4"/>
+      <c r="F176" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="G176" s="50" t="s">
+        <v>854</v>
+      </c>
+      <c r="H176" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="I176" s="6"/>
+    </row>
+    <row r="177" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B177" s="28" t="s">
+        <v>626</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="E177" s="4"/>
+      <c r="F177" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="G177" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H177" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="I177" s="6"/>
+    </row>
+    <row r="178" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B178" s="28" t="s">
+        <v>629</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="E178" s="4"/>
+      <c r="F178" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="G178" s="50" t="s">
+        <v>855</v>
+      </c>
+      <c r="H178" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="G175" s="3" t="s">
+      <c r="I178" s="6"/>
+    </row>
+    <row r="179" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A179" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B179" s="29" t="s">
         <v>633</v>
       </c>
-      <c r="H175" s="6"/>
-    </row>
-    <row r="176" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B176" s="29" t="s">
+      <c r="C179" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D179" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="C176" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D176" s="3" t="s">
+      <c r="E179" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="E176" s="3" t="s">
+      <c r="F179" s="4" t="s">
         <v>636</v>
       </c>
-      <c r="F176" s="4" t="s">
+      <c r="G179" s="50" t="s">
+        <v>856</v>
+      </c>
+      <c r="H179" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="G176" s="3" t="s">
+      <c r="I179" s="6"/>
+    </row>
+    <row r="180" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A180" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B180" s="29" t="s">
         <v>638</v>
       </c>
-      <c r="H176" s="6"/>
-    </row>
-    <row r="177" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B177" s="29" t="s">
+      <c r="C180" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D180" s="3" t="s">
         <v>639</v>
       </c>
-      <c r="C177" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D177" s="3" t="s">
+      <c r="E180" s="3"/>
+      <c r="F180" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="G180" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H180" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="E177" s="3"/>
-      <c r="F177" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="G177" s="3" t="s">
+      <c r="I180" s="6"/>
+    </row>
+    <row r="181" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B181" s="29" t="s">
         <v>641</v>
       </c>
-      <c r="H177" s="6"/>
-    </row>
-    <row r="178" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B178" s="29" t="s">
+      <c r="C181" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D181" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="C178" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D178" s="3" t="s">
+      <c r="E181" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="G181" s="50" t="s">
+        <v>856</v>
+      </c>
+      <c r="H181" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="E178" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="F178" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="G178" s="3" t="s">
+      <c r="I181" s="6"/>
+    </row>
+    <row r="182" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B182" s="29" t="s">
         <v>644</v>
       </c>
-      <c r="H178" s="6"/>
-    </row>
-    <row r="179" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B179" s="29" t="s">
+      <c r="C182" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D182" s="3" t="s">
         <v>645</v>
-      </c>
-      <c r="C179" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D179" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="E179" s="3"/>
-      <c r="F179" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="G179" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="H179" s="6"/>
-    </row>
-    <row r="180" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B180" s="29" t="s">
-        <v>648</v>
-      </c>
-      <c r="C180" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D180" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="E180" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="F180" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="G180" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="H180" s="6"/>
-    </row>
-    <row r="181" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B181" s="29" t="s">
-        <v>651</v>
-      </c>
-      <c r="C181" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D181" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="E181" s="3"/>
-      <c r="F181" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="G181" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="H181" s="6"/>
-    </row>
-    <row r="182" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B182" s="29" t="s">
-        <v>654</v>
-      </c>
-      <c r="C182" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D182" s="3" t="s">
-        <v>655</v>
       </c>
       <c r="E182" s="3"/>
       <c r="F182" s="4" t="s">
-        <v>656</v>
-      </c>
-      <c r="G182" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="H182" s="6"/>
-    </row>
-    <row r="183" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+      <c r="G182" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H182" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="I182" s="6"/>
+    </row>
+    <row r="183" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B183" s="29" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>659</v>
-      </c>
-      <c r="E183" s="3"/>
+        <v>648</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>635</v>
+      </c>
       <c r="F183" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="G183" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="H183" s="6"/>
-    </row>
-    <row r="184" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="38" t="s">
-        <v>662</v>
-      </c>
-      <c r="B184" s="35"/>
-      <c r="C184" s="35"/>
-      <c r="D184" s="35"/>
-      <c r="E184" s="35"/>
-      <c r="F184" s="35"/>
-      <c r="G184" s="35"/>
-      <c r="H184" s="36"/>
-    </row>
-    <row r="185" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>636</v>
+      </c>
+      <c r="G183" s="50" t="s">
+        <v>856</v>
+      </c>
+      <c r="H183" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="I183" s="6"/>
+    </row>
+    <row r="184" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B184" s="29" t="s">
+        <v>650</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="E184" s="3"/>
+      <c r="F184" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="G184" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H184" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="I184" s="6"/>
+    </row>
+    <row r="185" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="6" t="s">
-        <v>663</v>
+        <v>547</v>
       </c>
       <c r="B185" s="29" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>429</v>
+        <v>105</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="E185" s="3"/>
       <c r="F185" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="G185" s="50" t="s">
+        <v>857</v>
+      </c>
+      <c r="H185" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="I185" s="6"/>
+    </row>
+    <row r="186" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B186" s="29" t="s">
+        <v>657</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="E186" s="3"/>
+      <c r="F186" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="G186" s="50" t="s">
+        <v>854</v>
+      </c>
+      <c r="H186" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="I186" s="6"/>
+    </row>
+    <row r="187" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="48" t="s">
+        <v>661</v>
+      </c>
+      <c r="B187" s="36"/>
+      <c r="C187" s="36"/>
+      <c r="D187" s="36"/>
+      <c r="E187" s="36"/>
+      <c r="F187" s="36"/>
+      <c r="G187" s="36"/>
+      <c r="H187" s="36"/>
+      <c r="I187" s="37"/>
+    </row>
+    <row r="188" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B188" s="29" t="s">
+        <v>663</v>
+      </c>
+      <c r="C188" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="E188" s="3"/>
+      <c r="F188" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="G188" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="H188" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="G185" s="3" t="s">
+      <c r="I188" s="6"/>
+    </row>
+    <row r="189" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B189" s="28" t="s">
         <v>667</v>
       </c>
-      <c r="H185" s="6"/>
-    </row>
-    <row r="186" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="B186" s="28" t="s">
+      <c r="C189" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D189" s="4" t="s">
         <v>668</v>
       </c>
-      <c r="C186" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D186" s="4" t="s">
+      <c r="E189" s="4"/>
+      <c r="F189" s="4" t="s">
         <v>669</v>
       </c>
-      <c r="E186" s="4"/>
-      <c r="F186" s="4" t="s">
+      <c r="G189" s="50" t="s">
+        <v>858</v>
+      </c>
+      <c r="H189" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="G186" s="3" t="s">
+      <c r="I189" s="6"/>
+    </row>
+    <row r="190" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B190" s="27" t="s">
         <v>671</v>
       </c>
-      <c r="H186" s="6"/>
-    </row>
-    <row r="187" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="B187" s="27" t="s">
+      <c r="C190" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D190" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="C187" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D187" s="4" t="s">
+      <c r="E190" s="4" t="s">
         <v>673</v>
       </c>
-      <c r="E187" s="4" t="s">
+      <c r="F190" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="G190" s="50" t="s">
+        <v>854</v>
+      </c>
+      <c r="H190" s="12" t="s">
         <v>674</v>
       </c>
-      <c r="F187" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="G187" s="12" t="s">
+      <c r="I190" s="6"/>
+    </row>
+    <row r="191" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B191" s="28" t="s">
         <v>675</v>
       </c>
-      <c r="H187" s="6"/>
-    </row>
-    <row r="188" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="B188" s="28" t="s">
+      <c r="C191" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D191" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="C188" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D188" s="4" t="s">
+      <c r="E191" s="4"/>
+      <c r="F191" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="G191" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H191" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="E188" s="4"/>
-      <c r="F188" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="G188" s="3" t="s">
+      <c r="I191" s="6"/>
+    </row>
+    <row r="192" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A192" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B192" s="29" t="s">
         <v>678</v>
       </c>
-      <c r="H188" s="6"/>
-    </row>
-    <row r="189" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="B189" s="29" t="s">
+      <c r="C192" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D192" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="C189" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D189" s="3" t="s">
+      <c r="E192" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="E189" s="3" t="s">
+      <c r="F192" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="F189" s="4" t="s">
+      <c r="G192" s="50" t="s">
+        <v>859</v>
+      </c>
+      <c r="H192" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="G189" s="3" t="s">
+      <c r="I192" s="6"/>
+    </row>
+    <row r="193" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A193" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B193" s="29" t="s">
         <v>683</v>
       </c>
-      <c r="H189" s="6"/>
-    </row>
-    <row r="190" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="B190" s="29" t="s">
+      <c r="C193" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D193" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="C190" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D190" s="3" t="s">
+      <c r="E193" s="3"/>
+      <c r="F193" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="G193" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H193" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="E190" s="3"/>
-      <c r="F190" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="G190" s="3" t="s">
+      <c r="I193" s="6"/>
+    </row>
+    <row r="194" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A194" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B194" s="29" t="s">
         <v>686</v>
       </c>
-      <c r="H190" s="6"/>
-    </row>
-    <row r="191" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="B191" s="29" t="s">
+      <c r="C194" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D194" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="C191" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D191" s="3" t="s">
+      <c r="E194" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="F194" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="E191" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="F191" s="4" t="s">
+      <c r="G194" s="50" t="s">
+        <v>860</v>
+      </c>
+      <c r="H194" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="G191" s="3" t="s">
+      <c r="I194" s="6"/>
+    </row>
+    <row r="195" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A195" s="49" t="s">
         <v>690</v>
       </c>
-      <c r="H191" s="6"/>
-    </row>
-    <row r="192" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="39" t="s">
+      <c r="B195" s="36"/>
+      <c r="C195" s="36"/>
+      <c r="D195" s="36"/>
+      <c r="E195" s="36"/>
+      <c r="F195" s="36"/>
+      <c r="G195" s="36"/>
+      <c r="H195" s="36"/>
+      <c r="I195" s="37"/>
+    </row>
+    <row r="196" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B196" s="29" t="s">
         <v>691</v>
       </c>
-      <c r="B192" s="35"/>
-      <c r="C192" s="35"/>
-      <c r="D192" s="35"/>
-      <c r="E192" s="35"/>
-      <c r="F192" s="35"/>
-      <c r="G192" s="35"/>
-      <c r="H192" s="36"/>
-    </row>
-    <row r="193" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="B193" s="29" t="s">
+      <c r="C196" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D196" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="C193" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D193" s="3" t="s">
+      <c r="E196" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="E193" s="3" t="s">
+      <c r="F196" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="G196" s="50" t="s">
+        <v>854</v>
+      </c>
+      <c r="H196" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="F193" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="G193" s="3" t="s">
+      <c r="I196" s="6"/>
+    </row>
+    <row r="197" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B197" s="29" t="s">
         <v>695</v>
       </c>
-      <c r="H193" s="6"/>
-    </row>
-    <row r="194" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="B194" s="29" t="s">
+      <c r="C197" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D197" s="3" t="s">
         <v>696</v>
       </c>
-      <c r="C194" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D194" s="3" t="s">
+      <c r="E197" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="E194" s="3" t="s">
+      <c r="F197" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="G197" s="50" t="s">
+        <v>854</v>
+      </c>
+      <c r="H197" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="F194" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="G194" s="3" t="s">
+      <c r="I197" s="6"/>
+    </row>
+    <row r="198" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A198" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B198" s="29" t="s">
         <v>699</v>
       </c>
-      <c r="H194" s="6"/>
-    </row>
-    <row r="195" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="B195" s="29" t="s">
+      <c r="C198" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D198" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="C195" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D195" s="3" t="s">
+      <c r="E198" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="E195" s="3" t="s">
+      <c r="F198" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="F195" s="4" t="s">
+      <c r="G198" s="50" t="s">
+        <v>861</v>
+      </c>
+      <c r="H198" s="3" t="s">
         <v>703</v>
       </c>
-      <c r="G195" s="3" t="s">
+      <c r="I198" s="6"/>
+    </row>
+    <row r="199" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A199" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B199" s="29" t="s">
         <v>704</v>
       </c>
-      <c r="H195" s="6"/>
-    </row>
-    <row r="196" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="B196" s="29" t="s">
+      <c r="C199" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D199" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="C196" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D196" s="3" t="s">
+      <c r="E199" s="3"/>
+      <c r="F199" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="G199" s="50" t="s">
+        <v>854</v>
+      </c>
+      <c r="H199" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="E196" s="3"/>
-      <c r="F196" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="G196" s="3" t="s">
+      <c r="I199" s="6"/>
+    </row>
+    <row r="200" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A200" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B200" s="29" t="s">
         <v>707</v>
       </c>
-      <c r="H196" s="6"/>
-    </row>
-    <row r="197" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="B197" s="29" t="s">
+      <c r="C200" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D200" s="3" t="s">
         <v>708</v>
       </c>
-      <c r="C197" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D197" s="3" t="s">
+      <c r="E200" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="E197" s="3" t="s">
+      <c r="F200" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="G200" s="50" t="s">
+        <v>854</v>
+      </c>
+      <c r="H200" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="F197" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="G197" s="3" t="s">
+      <c r="I200" s="6"/>
+    </row>
+    <row r="201" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A201" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B201" s="28" t="s">
         <v>711</v>
       </c>
-      <c r="H197" s="6"/>
-    </row>
-    <row r="198" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="B198" s="28" t="s">
+      <c r="C201" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D201" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="C198" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D198" s="4" t="s">
+      <c r="E201" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="E198" s="4" t="s">
+      <c r="F201" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="G201" s="50" t="s">
+        <v>854</v>
+      </c>
+      <c r="H201" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="F198" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="G198" s="3" t="s">
+      <c r="I201" s="6"/>
+    </row>
+    <row r="202" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A202" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B202" s="27" t="s">
         <v>715</v>
       </c>
-      <c r="H198" s="6"/>
-    </row>
-    <row r="199" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="B199" s="27" t="s">
+      <c r="C202" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D202" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="C199" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D199" s="4" t="s">
+      <c r="E202" s="4" t="s">
         <v>717</v>
       </c>
-      <c r="E199" s="4" t="s">
+      <c r="F202" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="G202" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H202" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="F199" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="G199" s="3" t="s">
+      <c r="I202" s="6"/>
+    </row>
+    <row r="203" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A203" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B203" s="28" t="s">
         <v>719</v>
       </c>
-      <c r="H199" s="6"/>
-    </row>
-    <row r="200" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="B200" s="28" t="s">
+      <c r="C203" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D203" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="C200" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D200" s="4" t="s">
+      <c r="E203" s="4"/>
+      <c r="F203" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="G203" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H203" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="E200" s="4"/>
-      <c r="F200" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="G200" s="3" t="s">
+      <c r="I203" s="6"/>
+    </row>
+    <row r="204" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A204" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B204" s="29" t="s">
         <v>722</v>
       </c>
-      <c r="H200" s="6"/>
-    </row>
-    <row r="201" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="B201" s="29" t="s">
+      <c r="C204" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D204" s="3" t="s">
         <v>723</v>
       </c>
-      <c r="C201" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D201" s="3" t="s">
+      <c r="E204" s="3"/>
+      <c r="F204" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="E201" s="3"/>
-      <c r="F201" s="4" t="s">
+      <c r="G204" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H204" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="G201" s="3" t="s">
+      <c r="I204" s="6"/>
+    </row>
+    <row r="205" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A205" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B205" s="28" t="s">
         <v>726</v>
       </c>
-      <c r="H201" s="6"/>
-    </row>
-    <row r="202" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="B202" s="28" t="s">
+      <c r="C205" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D205" s="4" t="s">
         <v>727</v>
       </c>
-      <c r="C202" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D202" s="4" t="s">
+      <c r="E205" s="4"/>
+      <c r="F205" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="G205" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="H205" s="19" t="s">
         <v>728</v>
       </c>
-      <c r="E202" s="4"/>
-      <c r="F202" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="G202" s="19" t="s">
+      <c r="I205" s="3"/>
+    </row>
+    <row r="206" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A206" s="35" t="s">
         <v>729</v>
       </c>
-      <c r="H202" s="3"/>
-    </row>
-    <row r="203" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="34" t="s">
+      <c r="B206" s="36"/>
+      <c r="C206" s="36"/>
+      <c r="D206" s="36"/>
+      <c r="E206" s="36"/>
+      <c r="F206" s="36"/>
+      <c r="G206" s="36"/>
+      <c r="H206" s="36"/>
+      <c r="I206" s="37"/>
+    </row>
+    <row r="207" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A207" s="3" t="s">
         <v>730</v>
       </c>
-      <c r="B203" s="35"/>
-      <c r="C203" s="35"/>
-      <c r="D203" s="35"/>
-      <c r="E203" s="35"/>
-      <c r="F203" s="35"/>
-      <c r="G203" s="35"/>
-      <c r="H203" s="36"/>
-    </row>
-    <row r="204" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="3" t="s">
+      <c r="B207" s="32" t="s">
         <v>731</v>
       </c>
-      <c r="B204" s="32" t="s">
+      <c r="C207" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D207" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="C204" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="D204" s="3" t="s">
+      <c r="E207" s="3" t="s">
         <v>733</v>
       </c>
-      <c r="E204" s="3" t="s">
+      <c r="F207" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="G207" s="50" t="s">
+        <v>862</v>
+      </c>
+      <c r="H207" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="F204" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="G204" s="3" t="s">
-        <v>735</v>
-      </c>
-      <c r="H204" s="6"/>
+      <c r="I207" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A109:H109"/>
+    <mergeCell ref="A206:I206"/>
+    <mergeCell ref="A125:I125"/>
+    <mergeCell ref="A132:I132"/>
+    <mergeCell ref="A155:I155"/>
+    <mergeCell ref="A161:I161"/>
+    <mergeCell ref="A187:I187"/>
+    <mergeCell ref="A195:I195"/>
+    <mergeCell ref="A112:I112"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A71:H71"/>
-    <mergeCell ref="A81:H81"/>
-    <mergeCell ref="A89:H89"/>
-    <mergeCell ref="A99:H99"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A203:H203"/>
-    <mergeCell ref="A122:H122"/>
-    <mergeCell ref="A129:H129"/>
-    <mergeCell ref="A152:H152"/>
-    <mergeCell ref="A158:H158"/>
-    <mergeCell ref="A184:H184"/>
-    <mergeCell ref="A192:H192"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="A84:I84"/>
+    <mergeCell ref="A92:I92"/>
+    <mergeCell ref="A102:I102"/>
+    <mergeCell ref="A18:I18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
